--- a/Config/Datas/Tables/g_怪物_MonsterConfig.xlsx
+++ b/Config/Datas/Tables/g_怪物_MonsterConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbMonster" sheetId="1" r:id="R5460f4283c264430"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbMonster" sheetId="1" r:id="R5e6200f98d154461"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="116">
+  <x:cellXfs count="117">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -675,6 +675,13 @@
     </x:xf>
     <x:xf numFmtId="1" fontId="14" fillId="0" borderId="10" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -749,6 +756,23 @@
     </x:indexedColors>
   </x:colors>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -962,35 +986,23 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">visualSetId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">attributeProfileId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">defaultSkillId</x:t>
-        </x:is>
+      <x:c r="A1" s="89" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B1" s="89" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C1" s="89" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="D1" s="89" t="str">
+        <x:v>visualSetId</x:v>
+      </x:c>
+      <x:c r="E1" s="89" t="str">
+        <x:v>attributeProfileId</x:v>
+      </x:c>
+      <x:c r="F1" s="89" t="str">
+        <x:v>defaultSkillId</x:v>
       </x:c>
       <x:c r="G1" s="89" t="str">
         <x:v>bodyRadiusPixels</x:v>
@@ -1010,10 +1022,8 @@
       <x:c r="L1" s="89" t="str">
         <x:v>moveElevationPixels</x:v>
       </x:c>
-      <x:c r="M1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">movementType</x:t>
-        </x:is>
+      <x:c r="M1" s="89" t="str">
+        <x:v>movementType</x:v>
       </x:c>
       <x:c r="N1" t="str">
         <x:v>damageFloatHeightPixels</x:v>
@@ -1033,37 +1043,31 @@
       <x:c r="S1" t="str">
         <x:v>hitEffectOffsetYPixels</x:v>
       </x:c>
+      <x:c r="T1" t="str">
+        <x:v>isElite</x:v>
+      </x:c>
+      <x:c r="U1" t="str">
+        <x:v>deathChestProfileId</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int#ref=TbVisualSet</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?#ref=TbAttributeProfile</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?#ref=TbSkill</x:t>
-        </x:is>
+      <x:c r="A2" s="92" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B2" s="92" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C2" s="92" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D2" s="92" t="str">
+        <x:v>int#ref=TbVisualSet</x:v>
+      </x:c>
+      <x:c r="E2" s="92" t="str">
+        <x:v>int?#ref=TbAttributeProfile</x:v>
+      </x:c>
+      <x:c r="F2" s="92" t="str">
+        <x:v>int?#ref=TbSkill</x:v>
       </x:c>
       <x:c r="G2" s="92" t="str">
         <x:v>float?</x:v>
@@ -1083,10 +1087,8 @@
       <x:c r="L2" s="92" t="str">
         <x:v>float?</x:v>
       </x:c>
-      <x:c r="M2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EMovementType?</x:t>
-        </x:is>
+      <x:c r="M2" s="92" t="str">
+        <x:v>EMovementType?</x:v>
       </x:c>
       <x:c r="N2" t="str">
         <x:v>float?</x:v>
@@ -1106,61 +1108,56 @@
       <x:c r="S2" t="str">
         <x:v>float?</x:v>
       </x:c>
+      <x:c r="T2" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="U2" t="str">
+        <x:v>int?#ref=TbChestProfile</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="96" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="97" t="n"/>
-      <x:c r="C3" s="97" t="n"/>
-      <x:c r="D3" s="97" t="n"/>
-      <x:c r="E3" s="97" t="n"/>
-      <x:c r="F3" s="97" t="n"/>
-      <x:c r="G3" s="97" t="n"/>
-      <x:c r="H3" s="97" t="n"/>
-      <x:c r="I3" s="97" t="n"/>
-      <x:c r="J3" s="97" t="n"/>
-      <x:c r="K3" s="97" t="n"/>
-      <x:c r="L3" s="97" t="n"/>
-      <x:c r="M3" s="97" t="n"/>
+      <x:c r="A3" s="96" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B3" s="97"/>
+      <x:c r="C3" s="97"/>
+      <x:c r="D3" s="97"/>
+      <x:c r="E3" s="97"/>
+      <x:c r="F3" s="97"/>
+      <x:c r="G3" s="97"/>
+      <x:c r="H3" s="97"/>
+      <x:c r="I3" s="97"/>
+      <x:c r="J3" s="97"/>
+      <x:c r="K3" s="97"/>
+      <x:c r="L3" s="97"/>
+      <x:c r="M3" s="97"/>
+      <x:c r="N3"/>
       <x:c r="O3"/>
       <x:c r="P3"/>
       <x:c r="Q3"/>
       <x:c r="R3"/>
       <x:c r="S3"/>
+      <x:c r="T3"/>
+      <x:c r="U3"/>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="100" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">怪物ID：从10001开始递增</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">临时显示名，当前使用资源前缀</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">怪物表现集合ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">战斗属性方案；空值仅可预览</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">默认装备技能；不同于已解锁技能</x:t>
-        </x:is>
+      <x:c r="A4" s="100" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B4" s="101" t="str">
+        <x:v>怪物ID：从10001开始递增</x:v>
+      </x:c>
+      <x:c r="C4" s="101" t="str">
+        <x:v>临时显示名，当前使用资源前缀</x:v>
+      </x:c>
+      <x:c r="D4" s="101" t="str">
+        <x:v>怪物表现集合ID</x:v>
+      </x:c>
+      <x:c r="E4" s="101" t="str">
+        <x:v>战斗属性方案；空值仅可预览</x:v>
+      </x:c>
+      <x:c r="F4" s="101" t="str">
+        <x:v>默认装备技能；不同于已解锁技能</x:v>
       </x:c>
       <x:c r="G4" s="101" t="str">
         <x:v>受击判定半径；由怪物预制体“受击判定范围”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
@@ -1180,10 +1177,8 @@
       <x:c r="L4" s="101" t="str">
         <x:v>圆柱底面离地高度，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
-      <x:c r="M4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">移动分类；正式出战怪必填，资源目录行可空</x:t>
-        </x:is>
+      <x:c r="M4" s="101" t="str">
+        <x:v>移动分类；正式出战怪必填，资源目录行可空</x:v>
       </x:c>
       <x:c r="N4" t="str">
         <x:v>掉血/伤害数字浮动锚点高度；由预制体 DamageFloatAnchor 节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
@@ -1203,16 +1198,20 @@
       <x:c r="S4" t="str">
         <x:v>命中特效挂点纵向偏移；由怪物预制体“命中特效挂点”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
+      <x:c r="T4" t="str">
+        <x:v>独立精英身份，不触发最终Boss胜利</x:v>
+      </x:c>
+      <x:c r="U4" t="str">
+        <x:v>首次死亡在尸体位置掉箱</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="77" t="n"/>
+      <x:c r="A5" s="77"/>
       <x:c r="B5" s="115" t="n">
         <x:v>10001</x:v>
       </x:c>
-      <x:c r="C5" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm1</x:t>
-        </x:is>
+      <x:c r="C5" s="77" t="str">
+        <x:v>btm1</x:v>
       </x:c>
       <x:c r="D5" s="115" t="n">
         <x:v>20001</x:v>
@@ -1241,7 +1240,7 @@
       <x:c r="L5" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M5" s="77" t="n"/>
+      <x:c r="M5" s="77"/>
       <x:c r="N5" t="n">
         <x:v>179</x:v>
       </x:c>
@@ -1251,7 +1250,7 @@
       <x:c r="P5" t="n">
         <x:v>74.5</x:v>
       </x:c>
-      <x:c r="Q5">
+      <x:c r="Q5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R5" t="n">
@@ -1260,22 +1259,24 @@
       <x:c r="S5" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T5" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="77" t="n"/>
+      <x:c r="A6" s="77"/>
       <x:c r="B6" s="115" t="n">
         <x:v>10002</x:v>
       </x:c>
-      <x:c r="C6" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm2</x:t>
-        </x:is>
+      <x:c r="C6" s="77" t="str">
+        <x:v>btm2</x:v>
       </x:c>
       <x:c r="D6" s="115" t="n">
         <x:v>20002</x:v>
       </x:c>
-      <x:c r="E6" s="77" t="n"/>
-      <x:c r="F6" s="77" t="n"/>
+      <x:c r="E6" s="77"/>
+      <x:c r="F6" s="77"/>
       <x:c r="G6" t="n">
         <x:v>50</x:v>
       </x:c>
@@ -1294,7 +1295,7 @@
       <x:c r="L6" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="77" t="n"/>
+      <x:c r="M6" s="77"/>
       <x:c r="N6" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -1304,7 +1305,7 @@
       <x:c r="P6" t="n">
         <x:v>64.5</x:v>
       </x:c>
-      <x:c r="Q6">
+      <x:c r="Q6" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R6" t="n">
@@ -1313,22 +1314,24 @@
       <x:c r="S6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T6" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="77" t="n"/>
+      <x:c r="A7" s="77"/>
       <x:c r="B7" s="115" t="n">
         <x:v>10003</x:v>
       </x:c>
-      <x:c r="C7" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm101</x:t>
-        </x:is>
+      <x:c r="C7" s="77" t="str">
+        <x:v>btm101</x:v>
       </x:c>
       <x:c r="D7" s="115" t="n">
         <x:v>20003</x:v>
       </x:c>
-      <x:c r="E7" s="77" t="n"/>
-      <x:c r="F7" s="77" t="n"/>
+      <x:c r="E7" s="77"/>
+      <x:c r="F7" s="77"/>
       <x:c r="G7" t="n">
         <x:v>50</x:v>
       </x:c>
@@ -1347,7 +1350,7 @@
       <x:c r="L7" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M7" s="77" t="n"/>
+      <x:c r="M7" s="77"/>
       <x:c r="N7" t="n">
         <x:v>257</x:v>
       </x:c>
@@ -1357,7 +1360,7 @@
       <x:c r="P7" t="n">
         <x:v>60.8</x:v>
       </x:c>
-      <x:c r="Q7">
+      <x:c r="Q7" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R7" t="n">
@@ -1366,22 +1369,24 @@
       <x:c r="S7" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T7" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="77" t="n"/>
+      <x:c r="A8" s="77"/>
       <x:c r="B8" s="115" t="n">
         <x:v>10004</x:v>
       </x:c>
-      <x:c r="C8" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm102</x:t>
-        </x:is>
+      <x:c r="C8" s="77" t="str">
+        <x:v>btm102</x:v>
       </x:c>
       <x:c r="D8" s="115" t="n">
         <x:v>20004</x:v>
       </x:c>
-      <x:c r="E8" s="77" t="n"/>
-      <x:c r="F8" s="77" t="n"/>
+      <x:c r="E8" s="77"/>
+      <x:c r="F8" s="77"/>
       <x:c r="G8" t="n">
         <x:v>28.123</x:v>
       </x:c>
@@ -1400,7 +1405,7 @@
       <x:c r="L8" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M8" s="77" t="n"/>
+      <x:c r="M8" s="77"/>
       <x:c r="N8" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -1410,7 +1415,7 @@
       <x:c r="P8" t="n">
         <x:v>51.5</x:v>
       </x:c>
-      <x:c r="Q8">
+      <x:c r="Q8" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R8" t="n">
@@ -1419,22 +1424,24 @@
       <x:c r="S8" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T8" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="77" t="n"/>
+      <x:c r="A9" s="77"/>
       <x:c r="B9" s="115" t="n">
         <x:v>10005</x:v>
       </x:c>
-      <x:c r="C9" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm103</x:t>
-        </x:is>
+      <x:c r="C9" s="77" t="str">
+        <x:v>btm103</x:v>
       </x:c>
       <x:c r="D9" s="115" t="n">
         <x:v>20005</x:v>
       </x:c>
-      <x:c r="E9" s="77" t="n"/>
-      <x:c r="F9" s="77" t="n"/>
+      <x:c r="E9" s="77"/>
+      <x:c r="F9" s="77"/>
       <x:c r="G9" t="n">
         <x:v>38.18</x:v>
       </x:c>
@@ -1453,7 +1460,7 @@
       <x:c r="L9" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M9" s="77" t="n"/>
+      <x:c r="M9" s="77"/>
       <x:c r="N9" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -1463,7 +1470,7 @@
       <x:c r="P9" t="n">
         <x:v>61.3</x:v>
       </x:c>
-      <x:c r="Q9">
+      <x:c r="Q9" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R9" t="n">
@@ -1472,22 +1479,24 @@
       <x:c r="S9" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T9" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="77" t="n"/>
+      <x:c r="A10" s="77"/>
       <x:c r="B10" s="115" t="n">
         <x:v>10006</x:v>
       </x:c>
-      <x:c r="C10" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm104</x:t>
-        </x:is>
+      <x:c r="C10" s="77" t="str">
+        <x:v>btm104</x:v>
       </x:c>
       <x:c r="D10" s="115" t="n">
         <x:v>20006</x:v>
       </x:c>
-      <x:c r="E10" s="77" t="n"/>
-      <x:c r="F10" s="77" t="n"/>
+      <x:c r="E10" s="77"/>
+      <x:c r="F10" s="77"/>
       <x:c r="G10" t="n">
         <x:v>32.127</x:v>
       </x:c>
@@ -1506,7 +1515,7 @@
       <x:c r="L10" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="77" t="n"/>
+      <x:c r="M10" s="77"/>
       <x:c r="N10" t="n">
         <x:v>176</x:v>
       </x:c>
@@ -1516,7 +1525,7 @@
       <x:c r="P10" t="n">
         <x:v>63.6</x:v>
       </x:c>
-      <x:c r="Q10">
+      <x:c r="Q10" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R10" t="n">
@@ -1525,22 +1534,24 @@
       <x:c r="S10" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T10" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="77" t="n"/>
+      <x:c r="A11" s="77"/>
       <x:c r="B11" s="115" t="n">
         <x:v>10007</x:v>
       </x:c>
-      <x:c r="C11" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm105</x:t>
-        </x:is>
+      <x:c r="C11" s="77" t="str">
+        <x:v>btm105</x:v>
       </x:c>
       <x:c r="D11" s="115" t="n">
         <x:v>20007</x:v>
       </x:c>
-      <x:c r="E11" s="77" t="n"/>
-      <x:c r="F11" s="77" t="n"/>
+      <x:c r="E11" s="77"/>
+      <x:c r="F11" s="77"/>
       <x:c r="G11" t="n">
         <x:v>69</x:v>
       </x:c>
@@ -1559,7 +1570,7 @@
       <x:c r="L11" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="77" t="n"/>
+      <x:c r="M11" s="77"/>
       <x:c r="N11" t="n">
         <x:v>175</x:v>
       </x:c>
@@ -1569,7 +1580,7 @@
       <x:c r="P11" t="n">
         <x:v>72.5</x:v>
       </x:c>
-      <x:c r="Q11">
+      <x:c r="Q11" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R11" t="n">
@@ -1578,22 +1589,24 @@
       <x:c r="S11" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T11" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="77" t="n"/>
+      <x:c r="A12" s="77"/>
       <x:c r="B12" s="115" t="n">
         <x:v>10008</x:v>
       </x:c>
-      <x:c r="C12" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm106</x:t>
-        </x:is>
+      <x:c r="C12" s="77" t="str">
+        <x:v>btm106</x:v>
       </x:c>
       <x:c r="D12" s="115" t="n">
         <x:v>20008</x:v>
       </x:c>
-      <x:c r="E12" s="77" t="n"/>
-      <x:c r="F12" s="77" t="n"/>
+      <x:c r="E12" s="77"/>
+      <x:c r="F12" s="77"/>
       <x:c r="G12" t="n">
         <x:v>50</x:v>
       </x:c>
@@ -1612,7 +1625,7 @@
       <x:c r="L12" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="77" t="n"/>
+      <x:c r="M12" s="77"/>
       <x:c r="N12" t="n">
         <x:v>206</x:v>
       </x:c>
@@ -1622,7 +1635,7 @@
       <x:c r="P12" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="Q12">
+      <x:c r="Q12" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R12" t="n">
@@ -1631,22 +1644,24 @@
       <x:c r="S12" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T12" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="77" t="n"/>
+      <x:c r="A13" s="77"/>
       <x:c r="B13" s="115" t="n">
         <x:v>10009</x:v>
       </x:c>
-      <x:c r="C13" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm107</x:t>
-        </x:is>
+      <x:c r="C13" s="77" t="str">
+        <x:v>btm107</x:v>
       </x:c>
       <x:c r="D13" s="115" t="n">
         <x:v>20009</x:v>
       </x:c>
-      <x:c r="E13" s="77" t="n"/>
-      <x:c r="F13" s="77" t="n"/>
+      <x:c r="E13" s="77"/>
+      <x:c r="F13" s="77"/>
       <x:c r="G13" t="n">
         <x:v>51.505</x:v>
       </x:c>
@@ -1665,7 +1680,7 @@
       <x:c r="L13" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="77" t="n"/>
+      <x:c r="M13" s="77"/>
       <x:c r="N13" t="n">
         <x:v>200</x:v>
       </x:c>
@@ -1675,7 +1690,7 @@
       <x:c r="P13" t="n">
         <x:v>56.6</x:v>
       </x:c>
-      <x:c r="Q13">
+      <x:c r="Q13" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R13" t="n">
@@ -1684,16 +1699,18 @@
       <x:c r="S13" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T13" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="77" t="n"/>
+      <x:c r="A14" s="77"/>
       <x:c r="B14" s="115" t="n">
         <x:v>10010</x:v>
       </x:c>
-      <x:c r="C14" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm108</x:t>
-        </x:is>
+      <x:c r="C14" s="77" t="str">
+        <x:v>btm108</x:v>
       </x:c>
       <x:c r="D14" s="115" t="n">
         <x:v>20010</x:v>
@@ -1722,10 +1739,8 @@
       <x:c r="L14" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ground</x:t>
-        </x:is>
+      <x:c r="M14" s="77" t="str">
+        <x:v>Ground</x:v>
       </x:c>
       <x:c r="N14" t="n">
         <x:v>110</x:v>
@@ -1736,7 +1751,7 @@
       <x:c r="P14" t="n">
         <x:v>23.1</x:v>
       </x:c>
-      <x:c r="Q14">
+      <x:c r="Q14" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R14" t="n">
@@ -1745,16 +1760,18 @@
       <x:c r="S14" t="n">
         <x:v>23.1</x:v>
       </x:c>
+      <x:c r="T14" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="77" t="n"/>
+      <x:c r="A15" s="77"/>
       <x:c r="B15" s="115" t="n">
         <x:v>10011</x:v>
       </x:c>
-      <x:c r="C15" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm109</x:t>
-        </x:is>
+      <x:c r="C15" s="77" t="str">
+        <x:v>btm109</x:v>
       </x:c>
       <x:c r="D15" s="115" t="n">
         <x:v>20011</x:v>
@@ -1783,10 +1800,8 @@
       <x:c r="L15" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Flying</x:t>
-        </x:is>
+      <x:c r="M15" s="77" t="str">
+        <x:v>Flying</x:v>
       </x:c>
       <x:c r="N15" t="n">
         <x:v>130</x:v>
@@ -1797,7 +1812,7 @@
       <x:c r="P15" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="Q15">
+      <x:c r="Q15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R15" t="n">
@@ -1806,16 +1821,18 @@
       <x:c r="S15" t="n">
         <x:v>72</x:v>
       </x:c>
+      <x:c r="T15" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="77" t="n"/>
+      <x:c r="A16" s="77"/>
       <x:c r="B16" s="115" t="n">
         <x:v>10012</x:v>
       </x:c>
-      <x:c r="C16" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm110</x:t>
-        </x:is>
+      <x:c r="C16" s="77" t="str">
+        <x:v>btm110</x:v>
       </x:c>
       <x:c r="D16" s="115" t="n">
         <x:v>20012</x:v>
@@ -1844,10 +1861,8 @@
       <x:c r="L16" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ground</x:t>
-        </x:is>
+      <x:c r="M16" s="77" t="str">
+        <x:v>Ground</x:v>
       </x:c>
       <x:c r="N16" t="n">
         <x:v>141</x:v>
@@ -1858,7 +1873,7 @@
       <x:c r="P16" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="Q16">
+      <x:c r="Q16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R16" t="n">
@@ -1867,16 +1882,18 @@
       <x:c r="S16" t="n">
         <x:v>47</x:v>
       </x:c>
+      <x:c r="T16" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="77" t="n"/>
+      <x:c r="A17" s="77"/>
       <x:c r="B17" s="115" t="n">
         <x:v>10013</x:v>
       </x:c>
-      <x:c r="C17" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm111</x:t>
-        </x:is>
+      <x:c r="C17" s="77" t="str">
+        <x:v>btm111</x:v>
       </x:c>
       <x:c r="D17" s="115" t="n">
         <x:v>20013</x:v>
@@ -1905,10 +1922,8 @@
       <x:c r="L17" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ground</x:t>
-        </x:is>
+      <x:c r="M17" s="77" t="str">
+        <x:v>Ground</x:v>
       </x:c>
       <x:c r="N17" t="n">
         <x:v>150</x:v>
@@ -1919,7 +1934,7 @@
       <x:c r="P17" t="n">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="Q17">
+      <x:c r="Q17" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R17" t="n">
@@ -1928,22 +1943,28 @@
       <x:c r="S17" t="n">
         <x:v>87</x:v>
       </x:c>
+      <x:c r="T17" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U17"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="77" t="n"/>
+      <x:c r="A18" s="77"/>
       <x:c r="B18" s="115" t="n">
         <x:v>10014</x:v>
       </x:c>
-      <x:c r="C18" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm112</x:t>
-        </x:is>
+      <x:c r="C18" s="77" t="str">
+        <x:v>游荡者</x:v>
       </x:c>
       <x:c r="D18" s="115" t="n">
         <x:v>20014</x:v>
       </x:c>
-      <x:c r="E18" s="77" t="n"/>
-      <x:c r="F18" s="77" t="n"/>
+      <x:c r="E18" s="77" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F18" s="77" t="n">
+        <x:v>20002</x:v>
+      </x:c>
       <x:c r="G18" t="n">
         <x:v>51.51</x:v>
       </x:c>
@@ -1962,7 +1983,9 @@
       <x:c r="L18" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="77" t="n"/>
+      <x:c r="M18" s="77" t="str">
+        <x:v>Ground</x:v>
+      </x:c>
       <x:c r="N18" t="n">
         <x:v>243</x:v>
       </x:c>
@@ -1972,7 +1995,7 @@
       <x:c r="P18" t="n">
         <x:v>72.8</x:v>
       </x:c>
-      <x:c r="Q18">
+      <x:c r="Q18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R18" t="n">
@@ -1981,22 +2004,28 @@
       <x:c r="S18" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T18" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="77" t="n"/>
+      <x:c r="A19" s="77"/>
       <x:c r="B19" s="115" t="n">
         <x:v>10015</x:v>
       </x:c>
-      <x:c r="C19" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm113</x:t>
-        </x:is>
+      <x:c r="C19" s="77" t="str">
+        <x:v>坚甲卫</x:v>
       </x:c>
       <x:c r="D19" s="115" t="n">
         <x:v>20015</x:v>
       </x:c>
-      <x:c r="E19" s="77" t="n"/>
-      <x:c r="F19" s="77" t="n"/>
+      <x:c r="E19" s="77" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F19" s="77" t="n">
+        <x:v>20002</x:v>
+      </x:c>
       <x:c r="G19" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -2015,7 +2044,9 @@
       <x:c r="L19" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="77" t="n"/>
+      <x:c r="M19" s="77" t="str">
+        <x:v>Ground</x:v>
+      </x:c>
       <x:c r="N19" t="n">
         <x:v>202</x:v>
       </x:c>
@@ -2025,7 +2056,7 @@
       <x:c r="P19" t="n">
         <x:v>65.2</x:v>
       </x:c>
-      <x:c r="Q19">
+      <x:c r="Q19" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R19" t="n">
@@ -2034,22 +2065,28 @@
       <x:c r="S19" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T19" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="77" t="n"/>
+      <x:c r="A20" s="77"/>
       <x:c r="B20" s="115" t="n">
         <x:v>10016</x:v>
       </x:c>
-      <x:c r="C20" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm114</x:t>
-        </x:is>
+      <x:c r="C20" s="77" t="str">
+        <x:v>追猎者</x:v>
       </x:c>
       <x:c r="D20" s="115" t="n">
         <x:v>20016</x:v>
       </x:c>
-      <x:c r="E20" s="77" t="n"/>
-      <x:c r="F20" s="77" t="n"/>
+      <x:c r="E20" s="77" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F20" s="77" t="n">
+        <x:v>20002</x:v>
+      </x:c>
       <x:c r="G20" t="n">
         <x:v>44.142</x:v>
       </x:c>
@@ -2068,7 +2105,9 @@
       <x:c r="L20" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="77" t="n"/>
+      <x:c r="M20" s="77" t="str">
+        <x:v>Ground</x:v>
+      </x:c>
       <x:c r="N20" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -2078,7 +2117,7 @@
       <x:c r="P20" t="n">
         <x:v>63.2</x:v>
       </x:c>
-      <x:c r="Q20">
+      <x:c r="Q20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R20" t="n">
@@ -2087,22 +2126,28 @@
       <x:c r="S20" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T20" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="77" t="n"/>
+      <x:c r="A21" s="77"/>
       <x:c r="B21" s="115" t="n">
         <x:v>10017</x:v>
       </x:c>
-      <x:c r="C21" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm201</x:t>
-        </x:is>
+      <x:c r="C21" s="77" t="str">
+        <x:v>重甲卫</x:v>
       </x:c>
       <x:c r="D21" s="115" t="n">
         <x:v>20017</x:v>
       </x:c>
-      <x:c r="E21" s="77" t="n"/>
-      <x:c r="F21" s="77" t="n"/>
+      <x:c r="E21" s="77" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F21" s="77" t="n">
+        <x:v>20002</x:v>
+      </x:c>
       <x:c r="G21" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -2121,7 +2166,9 @@
       <x:c r="L21" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="77" t="n"/>
+      <x:c r="M21" s="77" t="str">
+        <x:v>Ground</x:v>
+      </x:c>
       <x:c r="N21" t="n">
         <x:v>200</x:v>
       </x:c>
@@ -2131,7 +2178,7 @@
       <x:c r="P21" t="n">
         <x:v>74.6</x:v>
       </x:c>
-      <x:c r="Q21">
+      <x:c r="Q21" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R21" t="n">
@@ -2140,22 +2187,28 @@
       <x:c r="S21" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T21" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U21"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="77" t="n"/>
+      <x:c r="A22" s="77"/>
       <x:c r="B22" s="115" t="n">
         <x:v>10018</x:v>
       </x:c>
-      <x:c r="C22" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm202</x:t>
-        </x:is>
+      <x:c r="C22" s="77" t="str">
+        <x:v>迅影精英</x:v>
       </x:c>
       <x:c r="D22" s="115" t="n">
         <x:v>20018</x:v>
       </x:c>
-      <x:c r="E22" s="77" t="n"/>
-      <x:c r="F22" s="77" t="n"/>
+      <x:c r="E22" s="77" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="77" t="n">
+        <x:v>29001</x:v>
+      </x:c>
       <x:c r="G22" t="n">
         <x:v>47.5</x:v>
       </x:c>
@@ -2174,7 +2227,9 @@
       <x:c r="L22" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="77" t="n"/>
+      <x:c r="M22" s="77" t="str">
+        <x:v>Ground</x:v>
+      </x:c>
       <x:c r="N22" t="n">
         <x:v>228</x:v>
       </x:c>
@@ -2184,7 +2239,7 @@
       <x:c r="P22" t="n">
         <x:v>68.3</x:v>
       </x:c>
-      <x:c r="Q22">
+      <x:c r="Q22" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R22" t="n">
@@ -2193,22 +2248,26 @@
       <x:c r="S22" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T22" s="116" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U22" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="77" t="n"/>
+      <x:c r="A23" s="77"/>
       <x:c r="B23" s="115" t="n">
         <x:v>10019</x:v>
       </x:c>
-      <x:c r="C23" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm203</x:t>
-        </x:is>
+      <x:c r="C23" s="77" t="str">
+        <x:v>btm203</x:v>
       </x:c>
       <x:c r="D23" s="115" t="n">
         <x:v>20019</x:v>
       </x:c>
-      <x:c r="E23" s="77" t="n"/>
-      <x:c r="F23" s="77" t="n"/>
+      <x:c r="E23" s="77"/>
+      <x:c r="F23" s="77"/>
       <x:c r="G23" t="n">
         <x:v>48.915</x:v>
       </x:c>
@@ -2227,7 +2286,7 @@
       <x:c r="L23" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="77" t="n"/>
+      <x:c r="M23" s="77"/>
       <x:c r="N23" t="n">
         <x:v>209</x:v>
       </x:c>
@@ -2237,7 +2296,7 @@
       <x:c r="P23" t="n">
         <x:v>61.9</x:v>
       </x:c>
-      <x:c r="Q23">
+      <x:c r="Q23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R23" t="n">
@@ -2246,22 +2305,24 @@
       <x:c r="S23" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T23" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U23"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="77" t="n"/>
+      <x:c r="A24" s="77"/>
       <x:c r="B24" s="115" t="n">
         <x:v>10020</x:v>
       </x:c>
-      <x:c r="C24" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm204</x:t>
-        </x:is>
+      <x:c r="C24" s="77" t="str">
+        <x:v>btm204</x:v>
       </x:c>
       <x:c r="D24" s="115" t="n">
         <x:v>20020</x:v>
       </x:c>
-      <x:c r="E24" s="77" t="n"/>
-      <x:c r="F24" s="77" t="n"/>
+      <x:c r="E24" s="77"/>
+      <x:c r="F24" s="77"/>
       <x:c r="G24" t="n">
         <x:v>51</x:v>
       </x:c>
@@ -2280,7 +2341,7 @@
       <x:c r="L24" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="77" t="n"/>
+      <x:c r="M24" s="77"/>
       <x:c r="N24" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -2290,7 +2351,7 @@
       <x:c r="P24" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="Q24">
+      <x:c r="Q24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R24" t="n">
@@ -2299,22 +2360,24 @@
       <x:c r="S24" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T24" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U24"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="77" t="n"/>
+      <x:c r="A25" s="77"/>
       <x:c r="B25" s="115" t="n">
         <x:v>10021</x:v>
       </x:c>
-      <x:c r="C25" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm209</x:t>
-        </x:is>
+      <x:c r="C25" s="77" t="str">
+        <x:v>btm209</x:v>
       </x:c>
       <x:c r="D25" s="115" t="n">
         <x:v>20021</x:v>
       </x:c>
-      <x:c r="E25" s="77" t="n"/>
-      <x:c r="F25" s="77" t="n"/>
+      <x:c r="E25" s="77"/>
+      <x:c r="F25" s="77"/>
       <x:c r="G25" t="n">
         <x:v>78</x:v>
       </x:c>
@@ -2333,7 +2396,7 @@
       <x:c r="L25" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="77" t="n"/>
+      <x:c r="M25" s="77"/>
       <x:c r="N25" t="n">
         <x:v>165</x:v>
       </x:c>
@@ -2343,7 +2406,7 @@
       <x:c r="P25" t="n">
         <x:v>67.5</x:v>
       </x:c>
-      <x:c r="Q25">
+      <x:c r="Q25" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R25" t="n">
@@ -2352,22 +2415,24 @@
       <x:c r="S25" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T25" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U25"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="77" t="n"/>
+      <x:c r="A26" s="77"/>
       <x:c r="B26" s="115" t="n">
         <x:v>10022</x:v>
       </x:c>
-      <x:c r="C26" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm210</x:t>
-        </x:is>
+      <x:c r="C26" s="77" t="str">
+        <x:v>btm210</x:v>
       </x:c>
       <x:c r="D26" s="115" t="n">
         <x:v>20022</x:v>
       </x:c>
-      <x:c r="E26" s="77" t="n"/>
-      <x:c r="F26" s="77" t="n"/>
+      <x:c r="E26" s="77"/>
+      <x:c r="F26" s="77"/>
       <x:c r="G26" t="n">
         <x:v>73.31</x:v>
       </x:c>
@@ -2386,7 +2451,7 @@
       <x:c r="L26" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="77" t="n"/>
+      <x:c r="M26" s="77"/>
       <x:c r="N26" t="n">
         <x:v>218</x:v>
       </x:c>
@@ -2396,7 +2461,7 @@
       <x:c r="P26" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="Q26">
+      <x:c r="Q26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R26" t="n">
@@ -2405,22 +2470,24 @@
       <x:c r="S26" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T26" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U26"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="77" t="n"/>
+      <x:c r="A27" s="77"/>
       <x:c r="B27" s="115" t="n">
         <x:v>10023</x:v>
       </x:c>
-      <x:c r="C27" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm211</x:t>
-        </x:is>
+      <x:c r="C27" s="77" t="str">
+        <x:v>btm211</x:v>
       </x:c>
       <x:c r="D27" s="115" t="n">
         <x:v>20023</x:v>
       </x:c>
-      <x:c r="E27" s="77" t="n"/>
-      <x:c r="F27" s="77" t="n"/>
+      <x:c r="E27" s="77"/>
+      <x:c r="F27" s="77"/>
       <x:c r="G27" t="n">
         <x:v>75.197</x:v>
       </x:c>
@@ -2439,7 +2506,7 @@
       <x:c r="L27" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="77" t="n"/>
+      <x:c r="M27" s="77"/>
       <x:c r="N27" t="n">
         <x:v>282</x:v>
       </x:c>
@@ -2449,7 +2516,7 @@
       <x:c r="P27" t="n">
         <x:v>84.5</x:v>
       </x:c>
-      <x:c r="Q27">
+      <x:c r="Q27" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R27" t="n">
@@ -2458,22 +2525,24 @@
       <x:c r="S27" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T27" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U27"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="77" t="n"/>
+      <x:c r="A28" s="77"/>
       <x:c r="B28" s="115" t="n">
         <x:v>10024</x:v>
       </x:c>
-      <x:c r="C28" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm212</x:t>
-        </x:is>
+      <x:c r="C28" s="77" t="str">
+        <x:v>btm212</x:v>
       </x:c>
       <x:c r="D28" s="115" t="n">
         <x:v>20024</x:v>
       </x:c>
-      <x:c r="E28" s="77" t="n"/>
-      <x:c r="F28" s="77" t="n"/>
+      <x:c r="E28" s="77"/>
+      <x:c r="F28" s="77"/>
       <x:c r="G28" t="n">
         <x:v>63.098</x:v>
       </x:c>
@@ -2492,7 +2561,7 @@
       <x:c r="L28" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="77" t="n"/>
+      <x:c r="M28" s="77"/>
       <x:c r="N28" t="n">
         <x:v>233</x:v>
       </x:c>
@@ -2502,7 +2571,7 @@
       <x:c r="P28" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="Q28">
+      <x:c r="Q28" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R28" t="n">
@@ -2511,22 +2580,24 @@
       <x:c r="S28" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T28" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U28"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="77" t="n"/>
+      <x:c r="A29" s="77"/>
       <x:c r="B29" s="115" t="n">
         <x:v>10025</x:v>
       </x:c>
-      <x:c r="C29" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm300</x:t>
-        </x:is>
+      <x:c r="C29" s="77" t="str">
+        <x:v>btm300</x:v>
       </x:c>
       <x:c r="D29" s="115" t="n">
         <x:v>20025</x:v>
       </x:c>
-      <x:c r="E29" s="77" t="n"/>
-      <x:c r="F29" s="77" t="n"/>
+      <x:c r="E29" s="77"/>
+      <x:c r="F29" s="77"/>
       <x:c r="G29" t="n">
         <x:v>67.081</x:v>
       </x:c>
@@ -2545,7 +2616,7 @@
       <x:c r="L29" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="77" t="n"/>
+      <x:c r="M29" s="77"/>
       <x:c r="N29" t="n">
         <x:v>228</x:v>
       </x:c>
@@ -2555,7 +2626,7 @@
       <x:c r="P29" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="Q29">
+      <x:c r="Q29" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R29" t="n">
@@ -2564,22 +2635,28 @@
       <x:c r="S29" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T29" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U29"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="77" t="n"/>
+      <x:c r="A30" s="77"/>
       <x:c r="B30" s="115" t="n">
         <x:v>10026</x:v>
       </x:c>
-      <x:c r="C30" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm301</x:t>
-        </x:is>
+      <x:c r="C30" s="77" t="str">
+        <x:v>镇域精英</x:v>
       </x:c>
       <x:c r="D30" s="115" t="n">
         <x:v>20026</x:v>
       </x:c>
-      <x:c r="E30" s="77" t="n"/>
-      <x:c r="F30" s="77" t="n"/>
+      <x:c r="E30" s="77" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F30" s="77" t="n">
+        <x:v>29002</x:v>
+      </x:c>
       <x:c r="G30" t="n">
         <x:v>54.5</x:v>
       </x:c>
@@ -2598,7 +2675,9 @@
       <x:c r="L30" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="77" t="n"/>
+      <x:c r="M30" s="77" t="str">
+        <x:v>Ground</x:v>
+      </x:c>
       <x:c r="N30" t="n">
         <x:v>171</x:v>
       </x:c>
@@ -2608,7 +2687,7 @@
       <x:c r="P30" t="n">
         <x:v>56.7</x:v>
       </x:c>
-      <x:c r="Q30">
+      <x:c r="Q30" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R30" t="n">
@@ -2617,22 +2696,26 @@
       <x:c r="S30" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T30" s="116" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U30" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="77" t="n"/>
+      <x:c r="A31" s="77"/>
       <x:c r="B31" s="115" t="n">
         <x:v>10027</x:v>
       </x:c>
-      <x:c r="C31" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm302</x:t>
-        </x:is>
+      <x:c r="C31" s="77" t="str">
+        <x:v>btm302</x:v>
       </x:c>
       <x:c r="D31" s="115" t="n">
         <x:v>20027</x:v>
       </x:c>
-      <x:c r="E31" s="77" t="n"/>
-      <x:c r="F31" s="77" t="n"/>
+      <x:c r="E31" s="77"/>
+      <x:c r="F31" s="77"/>
       <x:c r="G31" t="n">
         <x:v>41</x:v>
       </x:c>
@@ -2651,7 +2734,7 @@
       <x:c r="L31" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="77" t="n"/>
+      <x:c r="M31" s="77"/>
       <x:c r="N31" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -2661,7 +2744,7 @@
       <x:c r="P31" t="n">
         <x:v>63.9</x:v>
       </x:c>
-      <x:c r="Q31">
+      <x:c r="Q31" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R31" t="n">
@@ -2670,22 +2753,24 @@
       <x:c r="S31" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T31" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U31"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="77" t="n"/>
+      <x:c r="A32" s="77"/>
       <x:c r="B32" s="115" t="n">
         <x:v>10028</x:v>
       </x:c>
-      <x:c r="C32" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm303</x:t>
-        </x:is>
+      <x:c r="C32" s="77" t="str">
+        <x:v>btm303</x:v>
       </x:c>
       <x:c r="D32" s="115" t="n">
         <x:v>20028</x:v>
       </x:c>
-      <x:c r="E32" s="77" t="n"/>
-      <x:c r="F32" s="77" t="n"/>
+      <x:c r="E32" s="77"/>
+      <x:c r="F32" s="77"/>
       <x:c r="G32" t="n">
         <x:v>51.499</x:v>
       </x:c>
@@ -2704,7 +2789,7 @@
       <x:c r="L32" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="77" t="n"/>
+      <x:c r="M32" s="77"/>
       <x:c r="N32" t="n">
         <x:v>213</x:v>
       </x:c>
@@ -2714,7 +2799,7 @@
       <x:c r="P32" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="Q32">
+      <x:c r="Q32" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R32" t="n">
@@ -2723,22 +2808,24 @@
       <x:c r="S32" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T32" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U32"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="77" t="n"/>
+      <x:c r="A33" s="77"/>
       <x:c r="B33" s="115" t="n">
         <x:v>10029</x:v>
       </x:c>
-      <x:c r="C33" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm304</x:t>
-        </x:is>
+      <x:c r="C33" s="77" t="str">
+        <x:v>btm304</x:v>
       </x:c>
       <x:c r="D33" s="115" t="n">
         <x:v>20029</x:v>
       </x:c>
-      <x:c r="E33" s="77" t="n"/>
-      <x:c r="F33" s="77" t="n"/>
+      <x:c r="E33" s="77"/>
+      <x:c r="F33" s="77"/>
       <x:c r="G33" t="n">
         <x:v>43.5</x:v>
       </x:c>
@@ -2757,7 +2844,7 @@
       <x:c r="L33" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="77" t="n"/>
+      <x:c r="M33" s="77"/>
       <x:c r="N33" t="n">
         <x:v>217</x:v>
       </x:c>
@@ -2767,7 +2854,7 @@
       <x:c r="P33" t="n">
         <x:v>67.2</x:v>
       </x:c>
-      <x:c r="Q33">
+      <x:c r="Q33" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R33" t="n">
@@ -2776,22 +2863,24 @@
       <x:c r="S33" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T33" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U33"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="77" t="n"/>
+      <x:c r="A34" s="77"/>
       <x:c r="B34" s="115" t="n">
         <x:v>10030</x:v>
       </x:c>
-      <x:c r="C34" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm309</x:t>
-        </x:is>
+      <x:c r="C34" s="77" t="str">
+        <x:v>btm309</x:v>
       </x:c>
       <x:c r="D34" s="115" t="n">
         <x:v>20030</x:v>
       </x:c>
-      <x:c r="E34" s="77" t="n"/>
-      <x:c r="F34" s="77" t="n"/>
+      <x:c r="E34" s="77"/>
+      <x:c r="F34" s="77"/>
       <x:c r="G34" t="n">
         <x:v>45</x:v>
       </x:c>
@@ -2810,7 +2899,7 @@
       <x:c r="L34" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="77" t="n"/>
+      <x:c r="M34" s="77"/>
       <x:c r="N34" t="n">
         <x:v>177</x:v>
       </x:c>
@@ -2820,7 +2909,7 @@
       <x:c r="P34" t="n">
         <x:v>73.5</x:v>
       </x:c>
-      <x:c r="Q34">
+      <x:c r="Q34" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R34" t="n">
@@ -2829,22 +2918,24 @@
       <x:c r="S34" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T34" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U34"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="77" t="n"/>
+      <x:c r="A35" s="77"/>
       <x:c r="B35" s="115" t="n">
         <x:v>10031</x:v>
       </x:c>
-      <x:c r="C35" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm310</x:t>
-        </x:is>
+      <x:c r="C35" s="77" t="str">
+        <x:v>btm310</x:v>
       </x:c>
       <x:c r="D35" s="115" t="n">
         <x:v>20031</x:v>
       </x:c>
-      <x:c r="E35" s="77" t="n"/>
-      <x:c r="F35" s="77" t="n"/>
+      <x:c r="E35" s="77"/>
+      <x:c r="F35" s="77"/>
       <x:c r="G35" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -2863,7 +2954,7 @@
       <x:c r="L35" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="77" t="n"/>
+      <x:c r="M35" s="77"/>
       <x:c r="N35" t="n">
         <x:v>185</x:v>
       </x:c>
@@ -2873,7 +2964,7 @@
       <x:c r="P35" t="n">
         <x:v>61.5</x:v>
       </x:c>
-      <x:c r="Q35">
+      <x:c r="Q35" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R35" t="n">
@@ -2882,16 +2973,18 @@
       <x:c r="S35" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T35" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U35"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="77" t="n"/>
+      <x:c r="A36" s="77"/>
       <x:c r="B36" s="115" t="n">
         <x:v>10032</x:v>
       </x:c>
-      <x:c r="C36" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm311</x:t>
-        </x:is>
+      <x:c r="C36" s="77" t="str">
+        <x:v>btm311</x:v>
       </x:c>
       <x:c r="D36" s="115" t="n">
         <x:v>20032</x:v>
@@ -2920,10 +3013,8 @@
       <x:c r="L36" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M36" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ground</x:t>
-        </x:is>
+      <x:c r="M36" s="77" t="str">
+        <x:v>Ground</x:v>
       </x:c>
       <x:c r="N36" t="n">
         <x:v>283</x:v>
@@ -2934,7 +3025,7 @@
       <x:c r="P36" t="n">
         <x:v>80.2</x:v>
       </x:c>
-      <x:c r="Q36">
+      <x:c r="Q36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R36" t="n">
@@ -2943,22 +3034,24 @@
       <x:c r="S36" t="n">
         <x:v>80.2</x:v>
       </x:c>
+      <x:c r="T36" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U36"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="77" t="n"/>
+      <x:c r="A37" s="77"/>
       <x:c r="B37" s="115" t="n">
         <x:v>10033</x:v>
       </x:c>
-      <x:c r="C37" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm312</x:t>
-        </x:is>
+      <x:c r="C37" s="77" t="str">
+        <x:v>btm312</x:v>
       </x:c>
       <x:c r="D37" s="115" t="n">
         <x:v>20033</x:v>
       </x:c>
-      <x:c r="E37" s="77" t="n"/>
-      <x:c r="F37" s="77" t="n"/>
+      <x:c r="E37" s="77"/>
+      <x:c r="F37" s="77"/>
       <x:c r="G37" t="n">
         <x:v>72</x:v>
       </x:c>
@@ -2977,7 +3070,7 @@
       <x:c r="L37" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="77" t="n"/>
+      <x:c r="M37" s="77"/>
       <x:c r="N37" t="n">
         <x:v>246</x:v>
       </x:c>
@@ -2987,7 +3080,7 @@
       <x:c r="P37" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="Q37">
+      <x:c r="Q37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R37" t="n">
@@ -2996,22 +3089,24 @@
       <x:c r="S37" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T37" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U37"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="77" t="n"/>
+      <x:c r="A38" s="77"/>
       <x:c r="B38" s="115" t="n">
         <x:v>10034</x:v>
       </x:c>
-      <x:c r="C38" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm401</x:t>
-        </x:is>
+      <x:c r="C38" s="77" t="str">
+        <x:v>btm401</x:v>
       </x:c>
       <x:c r="D38" s="115" t="n">
         <x:v>20034</x:v>
       </x:c>
-      <x:c r="E38" s="77" t="n"/>
-      <x:c r="F38" s="77" t="n"/>
+      <x:c r="E38" s="77"/>
+      <x:c r="F38" s="77"/>
       <x:c r="G38" t="n">
         <x:v>62.5</x:v>
       </x:c>
@@ -3030,7 +3125,7 @@
       <x:c r="L38" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M38" s="77" t="n"/>
+      <x:c r="M38" s="77"/>
       <x:c r="N38" t="n">
         <x:v>225</x:v>
       </x:c>
@@ -3040,7 +3135,7 @@
       <x:c r="P38" t="n">
         <x:v>97.5</x:v>
       </x:c>
-      <x:c r="Q38">
+      <x:c r="Q38" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R38" t="n">
@@ -3049,22 +3144,24 @@
       <x:c r="S38" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T38" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U38"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="77" t="n"/>
+      <x:c r="A39" s="77"/>
       <x:c r="B39" s="115" t="n">
         <x:v>10035</x:v>
       </x:c>
-      <x:c r="C39" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm402</x:t>
-        </x:is>
+      <x:c r="C39" s="77" t="str">
+        <x:v>btm402</x:v>
       </x:c>
       <x:c r="D39" s="115" t="n">
         <x:v>20035</x:v>
       </x:c>
-      <x:c r="E39" s="77" t="n"/>
-      <x:c r="F39" s="77" t="n"/>
+      <x:c r="E39" s="77"/>
+      <x:c r="F39" s="77"/>
       <x:c r="G39" t="n">
         <x:v>52.482</x:v>
       </x:c>
@@ -3083,7 +3180,7 @@
       <x:c r="L39" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M39" s="77" t="n"/>
+      <x:c r="M39" s="77"/>
       <x:c r="N39" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -3093,7 +3190,7 @@
       <x:c r="P39" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="Q39">
+      <x:c r="Q39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R39" t="n">
@@ -3102,22 +3199,24 @@
       <x:c r="S39" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T39" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U39"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="77" t="n"/>
+      <x:c r="A40" s="77"/>
       <x:c r="B40" s="115" t="n">
         <x:v>10036</x:v>
       </x:c>
-      <x:c r="C40" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm403</x:t>
-        </x:is>
+      <x:c r="C40" s="77" t="str">
+        <x:v>btm403</x:v>
       </x:c>
       <x:c r="D40" s="115" t="n">
         <x:v>20036</x:v>
       </x:c>
-      <x:c r="E40" s="77" t="n"/>
-      <x:c r="F40" s="77" t="n"/>
+      <x:c r="E40" s="77"/>
+      <x:c r="F40" s="77"/>
       <x:c r="G40" t="n">
         <x:v>67</x:v>
       </x:c>
@@ -3136,7 +3235,7 @@
       <x:c r="L40" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M40" s="77" t="n"/>
+      <x:c r="M40" s="77"/>
       <x:c r="N40" t="n">
         <x:v>227</x:v>
       </x:c>
@@ -3146,7 +3245,7 @@
       <x:c r="P40" t="n">
         <x:v>74.8</x:v>
       </x:c>
-      <x:c r="Q40">
+      <x:c r="Q40" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R40" t="n">
@@ -3155,22 +3254,24 @@
       <x:c r="S40" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T40" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U40"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="77" t="n"/>
+      <x:c r="A41" s="77"/>
       <x:c r="B41" s="115" t="n">
         <x:v>10037</x:v>
       </x:c>
-      <x:c r="C41" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm404</x:t>
-        </x:is>
+      <x:c r="C41" s="77" t="str">
+        <x:v>btm404</x:v>
       </x:c>
       <x:c r="D41" s="115" t="n">
         <x:v>20037</x:v>
       </x:c>
-      <x:c r="E41" s="77" t="n"/>
-      <x:c r="F41" s="77" t="n"/>
+      <x:c r="E41" s="77"/>
+      <x:c r="F41" s="77"/>
       <x:c r="G41" t="n">
         <x:v>59.5</x:v>
       </x:c>
@@ -3189,7 +3290,7 @@
       <x:c r="L41" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M41" s="77" t="n"/>
+      <x:c r="M41" s="77"/>
       <x:c r="N41" t="n">
         <x:v>209</x:v>
       </x:c>
@@ -3199,7 +3300,7 @@
       <x:c r="P41" t="n">
         <x:v>51.8</x:v>
       </x:c>
-      <x:c r="Q41">
+      <x:c r="Q41" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R41" t="n">
@@ -3208,22 +3309,24 @@
       <x:c r="S41" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T41" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U41"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="77" t="n"/>
+      <x:c r="A42" s="77"/>
       <x:c r="B42" s="115" t="n">
         <x:v>10038</x:v>
       </x:c>
-      <x:c r="C42" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm409</x:t>
-        </x:is>
+      <x:c r="C42" s="77" t="str">
+        <x:v>btm409</x:v>
       </x:c>
       <x:c r="D42" s="115" t="n">
         <x:v>20038</x:v>
       </x:c>
-      <x:c r="E42" s="77" t="n"/>
-      <x:c r="F42" s="77" t="n"/>
+      <x:c r="E42" s="77"/>
+      <x:c r="F42" s="77"/>
       <x:c r="G42" t="n">
         <x:v>49.614</x:v>
       </x:c>
@@ -3242,7 +3345,7 @@
       <x:c r="L42" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M42" s="77" t="n"/>
+      <x:c r="M42" s="77"/>
       <x:c r="N42" t="n">
         <x:v>203</x:v>
       </x:c>
@@ -3252,7 +3355,7 @@
       <x:c r="P42" t="n">
         <x:v>67.9</x:v>
       </x:c>
-      <x:c r="Q42">
+      <x:c r="Q42" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R42" t="n">
@@ -3261,22 +3364,24 @@
       <x:c r="S42" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T42" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U42"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="77" t="n"/>
+      <x:c r="A43" s="77"/>
       <x:c r="B43" s="115" t="n">
         <x:v>10039</x:v>
       </x:c>
-      <x:c r="C43" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm410</x:t>
-        </x:is>
+      <x:c r="C43" s="77" t="str">
+        <x:v>btm410</x:v>
       </x:c>
       <x:c r="D43" s="115" t="n">
         <x:v>20039</x:v>
       </x:c>
-      <x:c r="E43" s="77" t="n"/>
-      <x:c r="F43" s="77" t="n"/>
+      <x:c r="E43" s="77"/>
+      <x:c r="F43" s="77"/>
       <x:c r="G43" t="n">
         <x:v>54.467</x:v>
       </x:c>
@@ -3295,7 +3400,7 @@
       <x:c r="L43" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M43" s="77" t="n"/>
+      <x:c r="M43" s="77"/>
       <x:c r="N43" t="n">
         <x:v>184</x:v>
       </x:c>
@@ -3305,7 +3410,7 @@
       <x:c r="P43" t="n">
         <x:v>57.7</x:v>
       </x:c>
-      <x:c r="Q43">
+      <x:c r="Q43" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R43" t="n">
@@ -3314,22 +3419,24 @@
       <x:c r="S43" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T43" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U43"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="77" t="n"/>
+      <x:c r="A44" s="77"/>
       <x:c r="B44" s="115" t="n">
         <x:v>10040</x:v>
       </x:c>
-      <x:c r="C44" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm411</x:t>
-        </x:is>
+      <x:c r="C44" s="77" t="str">
+        <x:v>btm411</x:v>
       </x:c>
       <x:c r="D44" s="115" t="n">
         <x:v>20040</x:v>
       </x:c>
-      <x:c r="E44" s="77" t="n"/>
-      <x:c r="F44" s="77" t="n"/>
+      <x:c r="E44" s="77"/>
+      <x:c r="F44" s="77"/>
       <x:c r="G44" t="n">
         <x:v>64.5</x:v>
       </x:c>
@@ -3348,7 +3455,7 @@
       <x:c r="L44" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M44" s="77" t="n"/>
+      <x:c r="M44" s="77"/>
       <x:c r="N44" t="n">
         <x:v>284</x:v>
       </x:c>
@@ -3358,7 +3465,7 @@
       <x:c r="P44" t="n">
         <x:v>80.1</x:v>
       </x:c>
-      <x:c r="Q44">
+      <x:c r="Q44" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R44" t="n">
@@ -3367,22 +3474,24 @@
       <x:c r="S44" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T44" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U44"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="77" t="n"/>
+      <x:c r="A45" s="77"/>
       <x:c r="B45" s="115" t="n">
         <x:v>10041</x:v>
       </x:c>
-      <x:c r="C45" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm412</x:t>
-        </x:is>
+      <x:c r="C45" s="77" t="str">
+        <x:v>btm412</x:v>
       </x:c>
       <x:c r="D45" s="115" t="n">
         <x:v>20041</x:v>
       </x:c>
-      <x:c r="E45" s="77" t="n"/>
-      <x:c r="F45" s="77" t="n"/>
+      <x:c r="E45" s="77"/>
+      <x:c r="F45" s="77"/>
       <x:c r="G45" t="n">
         <x:v>55.5</x:v>
       </x:c>
@@ -3401,7 +3510,7 @@
       <x:c r="L45" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M45" s="77" t="n"/>
+      <x:c r="M45" s="77"/>
       <x:c r="N45" t="n">
         <x:v>248</x:v>
       </x:c>
@@ -3411,7 +3520,7 @@
       <x:c r="P45" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="Q45">
+      <x:c r="Q45" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R45" t="n">
@@ -3420,22 +3529,24 @@
       <x:c r="S45" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T45" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U45"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="77" t="n"/>
+      <x:c r="A46" s="77"/>
       <x:c r="B46" s="115" t="n">
         <x:v>10042</x:v>
       </x:c>
-      <x:c r="C46" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm450</x:t>
-        </x:is>
+      <x:c r="C46" s="77" t="str">
+        <x:v>btm450</x:v>
       </x:c>
       <x:c r="D46" s="115" t="n">
         <x:v>20042</x:v>
       </x:c>
-      <x:c r="E46" s="77" t="n"/>
-      <x:c r="F46" s="77" t="n"/>
+      <x:c r="E46" s="77"/>
+      <x:c r="F46" s="77"/>
       <x:c r="G46" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -3454,7 +3565,7 @@
       <x:c r="L46" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M46" s="77" t="n"/>
+      <x:c r="M46" s="77"/>
       <x:c r="N46" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -3464,7 +3575,7 @@
       <x:c r="P46" t="n">
         <x:v>84.5</x:v>
       </x:c>
-      <x:c r="Q46">
+      <x:c r="Q46" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R46" t="n">
@@ -3473,22 +3584,24 @@
       <x:c r="S46" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T46" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U46"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="77" t="n"/>
+      <x:c r="A47" s="77"/>
       <x:c r="B47" s="115" t="n">
         <x:v>10043</x:v>
       </x:c>
-      <x:c r="C47" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm451_zd </x:t>
-        </x:is>
+      <x:c r="C47" s="77" t="str">
+        <x:v>btm451_zd </x:v>
       </x:c>
       <x:c r="D47" s="115" t="n">
         <x:v>20043</x:v>
       </x:c>
-      <x:c r="E47" s="77" t="n"/>
-      <x:c r="F47" s="77" t="n"/>
+      <x:c r="E47" s="77"/>
+      <x:c r="F47" s="77"/>
       <x:c r="G47" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -3507,7 +3620,7 @@
       <x:c r="L47" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M47" s="77" t="n"/>
+      <x:c r="M47" s="77"/>
       <x:c r="N47" t="n">
         <x:v>169</x:v>
       </x:c>
@@ -3517,7 +3630,7 @@
       <x:c r="P47" t="n">
         <x:v>69.5</x:v>
       </x:c>
-      <x:c r="Q47">
+      <x:c r="Q47" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R47" t="n">
@@ -3526,22 +3639,24 @@
       <x:c r="S47" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T47" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U47"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="77" t="n"/>
+      <x:c r="A48" s="77"/>
       <x:c r="B48" s="115" t="n">
         <x:v>10044</x:v>
       </x:c>
-      <x:c r="C48" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm501</x:t>
-        </x:is>
+      <x:c r="C48" s="77" t="str">
+        <x:v>btm501</x:v>
       </x:c>
       <x:c r="D48" s="115" t="n">
         <x:v>20044</x:v>
       </x:c>
-      <x:c r="E48" s="77" t="n"/>
-      <x:c r="F48" s="77" t="n"/>
+      <x:c r="E48" s="77"/>
+      <x:c r="F48" s="77"/>
       <x:c r="G48" t="n">
         <x:v>55</x:v>
       </x:c>
@@ -3560,7 +3675,7 @@
       <x:c r="L48" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M48" s="77" t="n"/>
+      <x:c r="M48" s="77"/>
       <x:c r="N48" t="n">
         <x:v>221</x:v>
       </x:c>
@@ -3570,7 +3685,7 @@
       <x:c r="P48" t="n">
         <x:v>75.7</x:v>
       </x:c>
-      <x:c r="Q48">
+      <x:c r="Q48" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R48" t="n">
@@ -3579,22 +3694,24 @@
       <x:c r="S48" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T48" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U48"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="77" t="n"/>
+      <x:c r="A49" s="77"/>
       <x:c r="B49" s="115" t="n">
         <x:v>10045</x:v>
       </x:c>
-      <x:c r="C49" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm502</x:t>
-        </x:is>
+      <x:c r="C49" s="77" t="str">
+        <x:v>btm502</x:v>
       </x:c>
       <x:c r="D49" s="115" t="n">
         <x:v>20045</x:v>
       </x:c>
-      <x:c r="E49" s="77" t="n"/>
-      <x:c r="F49" s="77" t="n"/>
+      <x:c r="E49" s="77"/>
+      <x:c r="F49" s="77"/>
       <x:c r="G49" t="n">
         <x:v>50.5</x:v>
       </x:c>
@@ -3613,7 +3730,7 @@
       <x:c r="L49" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M49" s="77" t="n"/>
+      <x:c r="M49" s="77"/>
       <x:c r="N49" t="n">
         <x:v>219</x:v>
       </x:c>
@@ -3623,7 +3740,7 @@
       <x:c r="P49" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="Q49">
+      <x:c r="Q49" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R49" t="n">
@@ -3632,22 +3749,24 @@
       <x:c r="S49" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T49" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U49"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="77" t="n"/>
+      <x:c r="A50" s="77"/>
       <x:c r="B50" s="115" t="n">
         <x:v>10046</x:v>
       </x:c>
-      <x:c r="C50" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm503</x:t>
-        </x:is>
+      <x:c r="C50" s="77" t="str">
+        <x:v>btm503</x:v>
       </x:c>
       <x:c r="D50" s="115" t="n">
         <x:v>20046</x:v>
       </x:c>
-      <x:c r="E50" s="77" t="n"/>
-      <x:c r="F50" s="77" t="n"/>
+      <x:c r="E50" s="77"/>
+      <x:c r="F50" s="77"/>
       <x:c r="G50" t="n">
         <x:v>70.943</x:v>
       </x:c>
@@ -3666,7 +3785,7 @@
       <x:c r="L50" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M50" s="77" t="n"/>
+      <x:c r="M50" s="77"/>
       <x:c r="N50" t="n">
         <x:v>290</x:v>
       </x:c>
@@ -3676,7 +3795,7 @@
       <x:c r="P50" t="n">
         <x:v>59.4</x:v>
       </x:c>
-      <x:c r="Q50">
+      <x:c r="Q50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R50" t="n">
@@ -3685,22 +3804,24 @@
       <x:c r="S50" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T50" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U50"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="77" t="n"/>
+      <x:c r="A51" s="77"/>
       <x:c r="B51" s="115" t="n">
         <x:v>10047</x:v>
       </x:c>
-      <x:c r="C51" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm504</x:t>
-        </x:is>
+      <x:c r="C51" s="77" t="str">
+        <x:v>btm504</x:v>
       </x:c>
       <x:c r="D51" s="115" t="n">
         <x:v>20047</x:v>
       </x:c>
-      <x:c r="E51" s="77" t="n"/>
-      <x:c r="F51" s="77" t="n"/>
+      <x:c r="E51" s="77"/>
+      <x:c r="F51" s="77"/>
       <x:c r="G51" t="n">
         <x:v>57.916</x:v>
       </x:c>
@@ -3719,7 +3840,7 @@
       <x:c r="L51" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M51" s="77" t="n"/>
+      <x:c r="M51" s="77"/>
       <x:c r="N51" t="n">
         <x:v>225</x:v>
       </x:c>
@@ -3729,7 +3850,7 @@
       <x:c r="P51" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="Q51">
+      <x:c r="Q51" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R51" t="n">
@@ -3738,22 +3859,24 @@
       <x:c r="S51" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T51" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U51"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="77" t="n"/>
+      <x:c r="A52" s="77"/>
       <x:c r="B52" s="115" t="n">
         <x:v>10048</x:v>
       </x:c>
-      <x:c r="C52" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm508</x:t>
-        </x:is>
+      <x:c r="C52" s="77" t="str">
+        <x:v>btm508</x:v>
       </x:c>
       <x:c r="D52" s="115" t="n">
         <x:v>20048</x:v>
       </x:c>
-      <x:c r="E52" s="77" t="n"/>
-      <x:c r="F52" s="77" t="n"/>
+      <x:c r="E52" s="77"/>
+      <x:c r="F52" s="77"/>
       <x:c r="G52" t="n">
         <x:v>114</x:v>
       </x:c>
@@ -3772,7 +3895,7 @@
       <x:c r="L52" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M52" s="77" t="n"/>
+      <x:c r="M52" s="77"/>
       <x:c r="N52" t="n">
         <x:v>248</x:v>
       </x:c>
@@ -3782,7 +3905,7 @@
       <x:c r="P52" t="n">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="Q52">
+      <x:c r="Q52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R52" t="n">
@@ -3791,22 +3914,24 @@
       <x:c r="S52" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T52" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U52"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="77" t="n"/>
+      <x:c r="A53" s="77"/>
       <x:c r="B53" s="115" t="n">
         <x:v>10049</x:v>
       </x:c>
-      <x:c r="C53" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm601</x:t>
-        </x:is>
+      <x:c r="C53" s="77" t="str">
+        <x:v>btm601</x:v>
       </x:c>
       <x:c r="D53" s="115" t="n">
         <x:v>20049</x:v>
       </x:c>
-      <x:c r="E53" s="77" t="n"/>
-      <x:c r="F53" s="77" t="n"/>
+      <x:c r="E53" s="77"/>
+      <x:c r="F53" s="77"/>
       <x:c r="G53" t="n">
         <x:v>109</x:v>
       </x:c>
@@ -3825,7 +3950,7 @@
       <x:c r="L53" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M53" s="77" t="n"/>
+      <x:c r="M53" s="77"/>
       <x:c r="N53" t="n">
         <x:v>218</x:v>
       </x:c>
@@ -3835,7 +3960,7 @@
       <x:c r="P53" t="n">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="Q53">
+      <x:c r="Q53" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R53" t="n">
@@ -3844,22 +3969,24 @@
       <x:c r="S53" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T53" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U53"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="77" t="n"/>
+      <x:c r="A54" s="77"/>
       <x:c r="B54" s="115" t="n">
         <x:v>10050</x:v>
       </x:c>
-      <x:c r="C54" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm602</x:t>
-        </x:is>
+      <x:c r="C54" s="77" t="str">
+        <x:v>btm602</x:v>
       </x:c>
       <x:c r="D54" s="115" t="n">
         <x:v>20050</x:v>
       </x:c>
-      <x:c r="E54" s="77" t="n"/>
-      <x:c r="F54" s="77" t="n"/>
+      <x:c r="E54" s="77"/>
+      <x:c r="F54" s="77"/>
       <x:c r="G54" t="n">
         <x:v>60</x:v>
       </x:c>
@@ -3878,7 +4005,7 @@
       <x:c r="L54" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M54" s="77" t="n"/>
+      <x:c r="M54" s="77"/>
       <x:c r="N54" t="n">
         <x:v>185</x:v>
       </x:c>
@@ -3888,7 +4015,7 @@
       <x:c r="P54" t="n">
         <x:v>77.5</x:v>
       </x:c>
-      <x:c r="Q54">
+      <x:c r="Q54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R54" t="n">
@@ -3897,22 +4024,24 @@
       <x:c r="S54" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T54" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U54"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="77" t="n"/>
+      <x:c r="A55" s="77"/>
       <x:c r="B55" s="115" t="n">
         <x:v>10051</x:v>
       </x:c>
-      <x:c r="C55" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm603</x:t>
-        </x:is>
+      <x:c r="C55" s="77" t="str">
+        <x:v>btm603</x:v>
       </x:c>
       <x:c r="D55" s="115" t="n">
         <x:v>20051</x:v>
       </x:c>
-      <x:c r="E55" s="77" t="n"/>
-      <x:c r="F55" s="77" t="n"/>
+      <x:c r="E55" s="77"/>
+      <x:c r="F55" s="77"/>
       <x:c r="G55" t="n">
         <x:v>37</x:v>
       </x:c>
@@ -3931,7 +4060,7 @@
       <x:c r="L55" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M55" s="77" t="n"/>
+      <x:c r="M55" s="77"/>
       <x:c r="N55" t="n">
         <x:v>186</x:v>
       </x:c>
@@ -3941,7 +4070,7 @@
       <x:c r="P55" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="Q55">
+      <x:c r="Q55" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R55" t="n">
@@ -3950,22 +4079,24 @@
       <x:c r="S55" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T55" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U55"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="77" t="n"/>
+      <x:c r="A56" s="77"/>
       <x:c r="B56" s="115" t="n">
         <x:v>10052</x:v>
       </x:c>
-      <x:c r="C56" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm604</x:t>
-        </x:is>
+      <x:c r="C56" s="77" t="str">
+        <x:v>btm604</x:v>
       </x:c>
       <x:c r="D56" s="115" t="n">
         <x:v>20052</x:v>
       </x:c>
-      <x:c r="E56" s="77" t="n"/>
-      <x:c r="F56" s="77" t="n"/>
+      <x:c r="E56" s="77"/>
+      <x:c r="F56" s="77"/>
       <x:c r="G56" t="n">
         <x:v>49</x:v>
       </x:c>
@@ -3984,7 +4115,7 @@
       <x:c r="L56" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M56" s="77" t="n"/>
+      <x:c r="M56" s="77"/>
       <x:c r="N56" t="n">
         <x:v>186</x:v>
       </x:c>
@@ -3994,7 +4125,7 @@
       <x:c r="P56" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="Q56">
+      <x:c r="Q56" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R56" t="n">
@@ -4003,22 +4134,24 @@
       <x:c r="S56" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T56" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U56"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="77" t="n"/>
+      <x:c r="A57" s="77"/>
       <x:c r="B57" s="115" t="n">
         <x:v>10053</x:v>
       </x:c>
-      <x:c r="C57" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm605</x:t>
-        </x:is>
+      <x:c r="C57" s="77" t="str">
+        <x:v>btm605</x:v>
       </x:c>
       <x:c r="D57" s="115" t="n">
         <x:v>20053</x:v>
       </x:c>
-      <x:c r="E57" s="77" t="n"/>
-      <x:c r="F57" s="77" t="n"/>
+      <x:c r="E57" s="77"/>
+      <x:c r="F57" s="77"/>
       <x:c r="G57" t="n">
         <x:v>132.5</x:v>
       </x:c>
@@ -4037,7 +4170,7 @@
       <x:c r="L57" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M57" s="77" t="n"/>
+      <x:c r="M57" s="77"/>
       <x:c r="N57" t="n">
         <x:v>303</x:v>
       </x:c>
@@ -4047,7 +4180,7 @@
       <x:c r="P57" t="n">
         <x:v>136.5</x:v>
       </x:c>
-      <x:c r="Q57">
+      <x:c r="Q57" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R57" t="n">
@@ -4056,22 +4189,24 @@
       <x:c r="S57" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T57" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U57"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="77" t="n"/>
+      <x:c r="A58" s="77"/>
       <x:c r="B58" s="115" t="n">
         <x:v>10054</x:v>
       </x:c>
-      <x:c r="C58" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm606</x:t>
-        </x:is>
+      <x:c r="C58" s="77" t="str">
+        <x:v>btm606</x:v>
       </x:c>
       <x:c r="D58" s="115" t="n">
         <x:v>20054</x:v>
       </x:c>
-      <x:c r="E58" s="77" t="n"/>
-      <x:c r="F58" s="77" t="n"/>
+      <x:c r="E58" s="77"/>
+      <x:c r="F58" s="77"/>
       <x:c r="G58" t="n">
         <x:v>47</x:v>
       </x:c>
@@ -4090,7 +4225,7 @@
       <x:c r="L58" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M58" s="77" t="n"/>
+      <x:c r="M58" s="77"/>
       <x:c r="N58" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -4100,7 +4235,7 @@
       <x:c r="P58" t="n">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="Q58">
+      <x:c r="Q58" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R58" t="n">
@@ -4109,22 +4244,24 @@
       <x:c r="S58" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T58" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U58"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="77" t="n"/>
+      <x:c r="A59" s="77"/>
       <x:c r="B59" s="115" t="n">
         <x:v>10055</x:v>
       </x:c>
-      <x:c r="C59" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm607</x:t>
-        </x:is>
+      <x:c r="C59" s="77" t="str">
+        <x:v>btm607</x:v>
       </x:c>
       <x:c r="D59" s="115" t="n">
         <x:v>20055</x:v>
       </x:c>
-      <x:c r="E59" s="77" t="n"/>
-      <x:c r="F59" s="77" t="n"/>
+      <x:c r="E59" s="77"/>
+      <x:c r="F59" s="77"/>
       <x:c r="G59" t="n">
         <x:v>38.5</x:v>
       </x:c>
@@ -4143,7 +4280,7 @@
       <x:c r="L59" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M59" s="77" t="n"/>
+      <x:c r="M59" s="77"/>
       <x:c r="N59" t="n">
         <x:v>210</x:v>
       </x:c>
@@ -4153,7 +4290,7 @@
       <x:c r="P59" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="Q59">
+      <x:c r="Q59" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R59" t="n">
@@ -4162,22 +4299,24 @@
       <x:c r="S59" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T59" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U59"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="77" t="n"/>
+      <x:c r="A60" s="77"/>
       <x:c r="B60" s="115" t="n">
         <x:v>10056</x:v>
       </x:c>
-      <x:c r="C60" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm701</x:t>
-        </x:is>
+      <x:c r="C60" s="77" t="str">
+        <x:v>btm701</x:v>
       </x:c>
       <x:c r="D60" s="115" t="n">
         <x:v>20056</x:v>
       </x:c>
-      <x:c r="E60" s="77" t="n"/>
-      <x:c r="F60" s="77" t="n"/>
+      <x:c r="E60" s="77"/>
+      <x:c r="F60" s="77"/>
       <x:c r="G60" t="n">
         <x:v>54.5</x:v>
       </x:c>
@@ -4196,7 +4335,7 @@
       <x:c r="L60" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M60" s="77" t="n"/>
+      <x:c r="M60" s="77"/>
       <x:c r="N60" t="n">
         <x:v>225</x:v>
       </x:c>
@@ -4206,7 +4345,7 @@
       <x:c r="P60" t="n">
         <x:v>97.5</x:v>
       </x:c>
-      <x:c r="Q60">
+      <x:c r="Q60" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R60" t="n">
@@ -4215,22 +4354,24 @@
       <x:c r="S60" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T60" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U60"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="77" t="n"/>
+      <x:c r="A61" s="77"/>
       <x:c r="B61" s="115" t="n">
         <x:v>10057</x:v>
       </x:c>
-      <x:c r="C61" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm702</x:t>
-        </x:is>
+      <x:c r="C61" s="77" t="str">
+        <x:v>btm702</x:v>
       </x:c>
       <x:c r="D61" s="115" t="n">
         <x:v>20057</x:v>
       </x:c>
-      <x:c r="E61" s="77" t="n"/>
-      <x:c r="F61" s="77" t="n"/>
+      <x:c r="E61" s="77"/>
+      <x:c r="F61" s="77"/>
       <x:c r="G61" t="n">
         <x:v>55.5</x:v>
       </x:c>
@@ -4249,7 +4390,7 @@
       <x:c r="L61" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M61" s="77" t="n"/>
+      <x:c r="M61" s="77"/>
       <x:c r="N61" t="n">
         <x:v>185</x:v>
       </x:c>
@@ -4259,7 +4400,7 @@
       <x:c r="P61" t="n">
         <x:v>77.5</x:v>
       </x:c>
-      <x:c r="Q61">
+      <x:c r="Q61" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R61" t="n">
@@ -4268,22 +4409,24 @@
       <x:c r="S61" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T61" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U61"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="77" t="n"/>
+      <x:c r="A62" s="77"/>
       <x:c r="B62" s="115" t="n">
         <x:v>10058</x:v>
       </x:c>
-      <x:c r="C62" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm703</x:t>
-        </x:is>
+      <x:c r="C62" s="77" t="str">
+        <x:v>btm703</x:v>
       </x:c>
       <x:c r="D62" s="115" t="n">
         <x:v>20058</x:v>
       </x:c>
-      <x:c r="E62" s="77" t="n"/>
-      <x:c r="F62" s="77" t="n"/>
+      <x:c r="E62" s="77"/>
+      <x:c r="F62" s="77"/>
       <x:c r="G62" t="n">
         <x:v>43.5</x:v>
       </x:c>
@@ -4302,7 +4445,7 @@
       <x:c r="L62" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M62" s="77" t="n"/>
+      <x:c r="M62" s="77"/>
       <x:c r="N62" t="n">
         <x:v>216</x:v>
       </x:c>
@@ -4312,7 +4455,7 @@
       <x:c r="P62" t="n">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="Q62">
+      <x:c r="Q62" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R62" t="n">
@@ -4321,22 +4464,24 @@
       <x:c r="S62" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T62" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U62"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="77" t="n"/>
+      <x:c r="A63" s="77"/>
       <x:c r="B63" s="115" t="n">
         <x:v>10059</x:v>
       </x:c>
-      <x:c r="C63" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm704</x:t>
-        </x:is>
+      <x:c r="C63" s="77" t="str">
+        <x:v>btm704</x:v>
       </x:c>
       <x:c r="D63" s="115" t="n">
         <x:v>20059</x:v>
       </x:c>
-      <x:c r="E63" s="77" t="n"/>
-      <x:c r="F63" s="77" t="n"/>
+      <x:c r="E63" s="77"/>
+      <x:c r="F63" s="77"/>
       <x:c r="G63" t="n">
         <x:v>56.5</x:v>
       </x:c>
@@ -4355,7 +4500,7 @@
       <x:c r="L63" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M63" s="77" t="n"/>
+      <x:c r="M63" s="77"/>
       <x:c r="N63" t="n">
         <x:v>201</x:v>
       </x:c>
@@ -4365,7 +4510,7 @@
       <x:c r="P63" t="n">
         <x:v>85.5</x:v>
       </x:c>
-      <x:c r="Q63">
+      <x:c r="Q63" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R63" t="n">
@@ -4374,22 +4519,24 @@
       <x:c r="S63" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T63" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U63"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="77" t="n"/>
+      <x:c r="A64" s="77"/>
       <x:c r="B64" s="115" t="n">
         <x:v>10060</x:v>
       </x:c>
-      <x:c r="C64" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm705</x:t>
-        </x:is>
+      <x:c r="C64" s="77" t="str">
+        <x:v>btm705</x:v>
       </x:c>
       <x:c r="D64" s="115" t="n">
         <x:v>20060</x:v>
       </x:c>
-      <x:c r="E64" s="77" t="n"/>
-      <x:c r="F64" s="77" t="n"/>
+      <x:c r="E64" s="77"/>
+      <x:c r="F64" s="77"/>
       <x:c r="G64" t="n">
         <x:v>129</x:v>
       </x:c>
@@ -4408,7 +4555,7 @@
       <x:c r="L64" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M64" s="77" t="n"/>
+      <x:c r="M64" s="77"/>
       <x:c r="N64" t="n">
         <x:v>245</x:v>
       </x:c>
@@ -4418,7 +4565,7 @@
       <x:c r="P64" t="n">
         <x:v>107.5</x:v>
       </x:c>
-      <x:c r="Q64">
+      <x:c r="Q64" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R64" t="n">
@@ -4427,22 +4574,24 @@
       <x:c r="S64" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T64" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U64"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="77" t="n"/>
+      <x:c r="A65" s="77"/>
       <x:c r="B65" s="115" t="n">
         <x:v>10061</x:v>
       </x:c>
-      <x:c r="C65" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm801</x:t>
-        </x:is>
+      <x:c r="C65" s="77" t="str">
+        <x:v>btm801</x:v>
       </x:c>
       <x:c r="D65" s="115" t="n">
         <x:v>20061</x:v>
       </x:c>
-      <x:c r="E65" s="77" t="n"/>
-      <x:c r="F65" s="77" t="n"/>
+      <x:c r="E65" s="77"/>
+      <x:c r="F65" s="77"/>
       <x:c r="G65" t="n">
         <x:v>99</x:v>
       </x:c>
@@ -4461,7 +4610,7 @@
       <x:c r="L65" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M65" s="77" t="n"/>
+      <x:c r="M65" s="77"/>
       <x:c r="N65" t="n">
         <x:v>218</x:v>
       </x:c>
@@ -4471,7 +4620,7 @@
       <x:c r="P65" t="n">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="Q65">
+      <x:c r="Q65" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R65" t="n">
@@ -4480,22 +4629,24 @@
       <x:c r="S65" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T65" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U65"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="77" t="n"/>
+      <x:c r="A66" s="77"/>
       <x:c r="B66" s="115" t="n">
         <x:v>10062</x:v>
       </x:c>
-      <x:c r="C66" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm802</x:t>
-        </x:is>
+      <x:c r="C66" s="77" t="str">
+        <x:v>btm802</x:v>
       </x:c>
       <x:c r="D66" s="115" t="n">
         <x:v>20062</x:v>
       </x:c>
-      <x:c r="E66" s="77" t="n"/>
-      <x:c r="F66" s="77" t="n"/>
+      <x:c r="E66" s="77"/>
+      <x:c r="F66" s="77"/>
       <x:c r="G66" t="n">
         <x:v>106</x:v>
       </x:c>
@@ -4514,7 +4665,7 @@
       <x:c r="L66" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M66" s="77" t="n"/>
+      <x:c r="M66" s="77"/>
       <x:c r="N66" t="n">
         <x:v>246</x:v>
       </x:c>
@@ -4524,7 +4675,7 @@
       <x:c r="P66" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="Q66">
+      <x:c r="Q66" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R66" t="n">
@@ -4533,22 +4684,24 @@
       <x:c r="S66" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T66" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U66"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="77" t="n"/>
+      <x:c r="A67" s="77"/>
       <x:c r="B67" s="115" t="n">
         <x:v>10063</x:v>
       </x:c>
-      <x:c r="C67" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm803</x:t>
-        </x:is>
+      <x:c r="C67" s="77" t="str">
+        <x:v>btm803</x:v>
       </x:c>
       <x:c r="D67" s="115" t="n">
         <x:v>20063</x:v>
       </x:c>
-      <x:c r="E67" s="77" t="n"/>
-      <x:c r="F67" s="77" t="n"/>
+      <x:c r="E67" s="77"/>
+      <x:c r="F67" s="77"/>
       <x:c r="G67" t="n">
         <x:v>63</x:v>
       </x:c>
@@ -4567,7 +4720,7 @@
       <x:c r="L67" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M67" s="77" t="n"/>
+      <x:c r="M67" s="77"/>
       <x:c r="N67" t="n">
         <x:v>207</x:v>
       </x:c>
@@ -4577,7 +4730,7 @@
       <x:c r="P67" t="n">
         <x:v>88.5</x:v>
       </x:c>
-      <x:c r="Q67">
+      <x:c r="Q67" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R67" t="n">
@@ -4586,22 +4739,24 @@
       <x:c r="S67" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T67" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U67"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="77" t="n"/>
+      <x:c r="A68" s="77"/>
       <x:c r="B68" s="115" t="n">
         <x:v>10064</x:v>
       </x:c>
-      <x:c r="C68" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm804</x:t>
-        </x:is>
+      <x:c r="C68" s="77" t="str">
+        <x:v>btm804</x:v>
       </x:c>
       <x:c r="D68" s="115" t="n">
         <x:v>20064</x:v>
       </x:c>
-      <x:c r="E68" s="77" t="n"/>
-      <x:c r="F68" s="77" t="n"/>
+      <x:c r="E68" s="77"/>
+      <x:c r="F68" s="77"/>
       <x:c r="G68" t="n">
         <x:v>52.5</x:v>
       </x:c>
@@ -4620,7 +4775,7 @@
       <x:c r="L68" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M68" s="77" t="n"/>
+      <x:c r="M68" s="77"/>
       <x:c r="N68" t="n">
         <x:v>205</x:v>
       </x:c>
@@ -4630,7 +4785,7 @@
       <x:c r="P68" t="n">
         <x:v>87.5</x:v>
       </x:c>
-      <x:c r="Q68">
+      <x:c r="Q68" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R68" t="n">
@@ -4639,22 +4794,24 @@
       <x:c r="S68" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T68" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U68"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="77" t="n"/>
+      <x:c r="A69" s="77"/>
       <x:c r="B69" s="115" t="n">
         <x:v>10065</x:v>
       </x:c>
-      <x:c r="C69" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm901</x:t>
-        </x:is>
+      <x:c r="C69" s="77" t="str">
+        <x:v>btm901</x:v>
       </x:c>
       <x:c r="D69" s="115" t="n">
         <x:v>20065</x:v>
       </x:c>
-      <x:c r="E69" s="77" t="n"/>
-      <x:c r="F69" s="77" t="n"/>
+      <x:c r="E69" s="77"/>
+      <x:c r="F69" s="77"/>
       <x:c r="G69" t="n">
         <x:v>77.5</x:v>
       </x:c>
@@ -4673,7 +4830,7 @@
       <x:c r="L69" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M69" s="77" t="n"/>
+      <x:c r="M69" s="77"/>
       <x:c r="N69" t="n">
         <x:v>183</x:v>
       </x:c>
@@ -4683,7 +4840,7 @@
       <x:c r="P69" t="n">
         <x:v>76.5</x:v>
       </x:c>
-      <x:c r="Q69">
+      <x:c r="Q69" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R69" t="n">
@@ -4692,22 +4849,24 @@
       <x:c r="S69" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T69" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U69"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="77" t="n"/>
+      <x:c r="A70" s="77"/>
       <x:c r="B70" s="115" t="n">
         <x:v>10066</x:v>
       </x:c>
-      <x:c r="C70" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm902</x:t>
-        </x:is>
+      <x:c r="C70" s="77" t="str">
+        <x:v>btm902</x:v>
       </x:c>
       <x:c r="D70" s="115" t="n">
         <x:v>20066</x:v>
       </x:c>
-      <x:c r="E70" s="77" t="n"/>
-      <x:c r="F70" s="77" t="n"/>
+      <x:c r="E70" s="77"/>
+      <x:c r="F70" s="77"/>
       <x:c r="G70" t="n">
         <x:v>56.5</x:v>
       </x:c>
@@ -4726,7 +4885,7 @@
       <x:c r="L70" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M70" s="77" t="n"/>
+      <x:c r="M70" s="77"/>
       <x:c r="N70" t="n">
         <x:v>213</x:v>
       </x:c>
@@ -4736,7 +4895,7 @@
       <x:c r="P70" t="n">
         <x:v>91.5</x:v>
       </x:c>
-      <x:c r="Q70">
+      <x:c r="Q70" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R70" t="n">
@@ -4745,22 +4904,24 @@
       <x:c r="S70" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T70" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U70"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="77" t="n"/>
+      <x:c r="A71" s="77"/>
       <x:c r="B71" s="115" t="n">
         <x:v>10067</x:v>
       </x:c>
-      <x:c r="C71" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm903</x:t>
-        </x:is>
+      <x:c r="C71" s="77" t="str">
+        <x:v>btm903</x:v>
       </x:c>
       <x:c r="D71" s="115" t="n">
         <x:v>20067</x:v>
       </x:c>
-      <x:c r="E71" s="77" t="n"/>
-      <x:c r="F71" s="77" t="n"/>
+      <x:c r="E71" s="77"/>
+      <x:c r="F71" s="77"/>
       <x:c r="G71" t="n">
         <x:v>60.5</x:v>
       </x:c>
@@ -4779,7 +4940,7 @@
       <x:c r="L71" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M71" s="77" t="n"/>
+      <x:c r="M71" s="77"/>
       <x:c r="N71" t="n">
         <x:v>222</x:v>
       </x:c>
@@ -4789,7 +4950,7 @@
       <x:c r="P71" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="Q71">
+      <x:c r="Q71" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R71" t="n">
@@ -4798,22 +4959,24 @@
       <x:c r="S71" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T71" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U71"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="77" t="n"/>
+      <x:c r="A72" s="77"/>
       <x:c r="B72" s="115" t="n">
         <x:v>10068</x:v>
       </x:c>
-      <x:c r="C72" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm904</x:t>
-        </x:is>
+      <x:c r="C72" s="77" t="str">
+        <x:v>btm904</x:v>
       </x:c>
       <x:c r="D72" s="115" t="n">
         <x:v>20068</x:v>
       </x:c>
-      <x:c r="E72" s="77" t="n"/>
-      <x:c r="F72" s="77" t="n"/>
+      <x:c r="E72" s="77"/>
+      <x:c r="F72" s="77"/>
       <x:c r="G72" t="n">
         <x:v>68.5</x:v>
       </x:c>
@@ -4832,7 +4995,7 @@
       <x:c r="L72" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M72" s="77" t="n"/>
+      <x:c r="M72" s="77"/>
       <x:c r="N72" t="n">
         <x:v>169</x:v>
       </x:c>
@@ -4842,7 +5005,7 @@
       <x:c r="P72" t="n">
         <x:v>69.5</x:v>
       </x:c>
-      <x:c r="Q72">
+      <x:c r="Q72" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R72" t="n">
@@ -4851,22 +5014,24 @@
       <x:c r="S72" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T72" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U72"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="77" t="n"/>
+      <x:c r="A73" s="77"/>
       <x:c r="B73" s="115" t="n">
         <x:v>10069</x:v>
       </x:c>
-      <x:c r="C73" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm905</x:t>
-        </x:is>
+      <x:c r="C73" s="77" t="str">
+        <x:v>btm905</x:v>
       </x:c>
       <x:c r="D73" s="115" t="n">
         <x:v>20069</x:v>
       </x:c>
-      <x:c r="E73" s="77" t="n"/>
-      <x:c r="F73" s="77" t="n"/>
+      <x:c r="E73" s="77"/>
+      <x:c r="F73" s="77"/>
       <x:c r="G73" t="n">
         <x:v>59.5</x:v>
       </x:c>
@@ -4885,7 +5050,7 @@
       <x:c r="L73" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M73" s="77" t="n"/>
+      <x:c r="M73" s="77"/>
       <x:c r="N73" t="n">
         <x:v>224</x:v>
       </x:c>
@@ -4895,7 +5060,7 @@
       <x:c r="P73" t="n">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="Q73">
+      <x:c r="Q73" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R73" t="n">
@@ -4904,22 +5069,24 @@
       <x:c r="S73" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T73" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U73"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="77" t="n"/>
+      <x:c r="A74" s="77"/>
       <x:c r="B74" s="115" t="n">
         <x:v>10070</x:v>
       </x:c>
-      <x:c r="C74" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm906</x:t>
-        </x:is>
+      <x:c r="C74" s="77" t="str">
+        <x:v>btm906</x:v>
       </x:c>
       <x:c r="D74" s="115" t="n">
         <x:v>20070</x:v>
       </x:c>
-      <x:c r="E74" s="77" t="n"/>
-      <x:c r="F74" s="77" t="n"/>
+      <x:c r="E74" s="77"/>
+      <x:c r="F74" s="77"/>
       <x:c r="G74" t="n">
         <x:v>73</x:v>
       </x:c>
@@ -4938,7 +5105,7 @@
       <x:c r="L74" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M74" s="77" t="n"/>
+      <x:c r="M74" s="77"/>
       <x:c r="N74" t="n">
         <x:v>206</x:v>
       </x:c>
@@ -4948,7 +5115,7 @@
       <x:c r="P74" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="Q74">
+      <x:c r="Q74" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R74" t="n">
@@ -4957,22 +5124,24 @@
       <x:c r="S74" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T74" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U74"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="77" t="n"/>
+      <x:c r="A75" s="77"/>
       <x:c r="B75" s="115" t="n">
         <x:v>10071</x:v>
       </x:c>
-      <x:c r="C75" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm907</x:t>
-        </x:is>
+      <x:c r="C75" s="77" t="str">
+        <x:v>btm907</x:v>
       </x:c>
       <x:c r="D75" s="115" t="n">
         <x:v>20071</x:v>
       </x:c>
-      <x:c r="E75" s="77" t="n"/>
-      <x:c r="F75" s="77" t="n"/>
+      <x:c r="E75" s="77"/>
+      <x:c r="F75" s="77"/>
       <x:c r="G75" t="n">
         <x:v>35.5</x:v>
       </x:c>
@@ -4991,7 +5160,7 @@
       <x:c r="L75" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M75" s="77" t="n"/>
+      <x:c r="M75" s="77"/>
       <x:c r="N75" t="n">
         <x:v>214</x:v>
       </x:c>
@@ -5001,7 +5170,7 @@
       <x:c r="P75" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="Q75">
+      <x:c r="Q75" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R75" t="n">
@@ -5010,22 +5179,24 @@
       <x:c r="S75" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T75" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U75"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="77" t="n"/>
+      <x:c r="A76" s="77"/>
       <x:c r="B76" s="115" t="n">
         <x:v>10072</x:v>
       </x:c>
-      <x:c r="C76" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm908</x:t>
-        </x:is>
+      <x:c r="C76" s="77" t="str">
+        <x:v>btm908</x:v>
       </x:c>
       <x:c r="D76" s="115" t="n">
         <x:v>20072</x:v>
       </x:c>
-      <x:c r="E76" s="77" t="n"/>
-      <x:c r="F76" s="77" t="n"/>
+      <x:c r="E76" s="77"/>
+      <x:c r="F76" s="77"/>
       <x:c r="G76" t="n">
         <x:v>38.5</x:v>
       </x:c>
@@ -5044,7 +5215,7 @@
       <x:c r="L76" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M76" s="77" t="n"/>
+      <x:c r="M76" s="77"/>
       <x:c r="N76" t="n">
         <x:v>181</x:v>
       </x:c>
@@ -5054,7 +5225,7 @@
       <x:c r="P76" t="n">
         <x:v>75.5</x:v>
       </x:c>
-      <x:c r="Q76">
+      <x:c r="Q76" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R76" t="n">
@@ -5063,22 +5234,24 @@
       <x:c r="S76" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T76" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U76"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="77" t="n"/>
+      <x:c r="A77" s="77"/>
       <x:c r="B77" s="115" t="n">
         <x:v>10073</x:v>
       </x:c>
-      <x:c r="C77" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm909</x:t>
-        </x:is>
+      <x:c r="C77" s="77" t="str">
+        <x:v>btm909</x:v>
       </x:c>
       <x:c r="D77" s="115" t="n">
         <x:v>20073</x:v>
       </x:c>
-      <x:c r="E77" s="77" t="n"/>
-      <x:c r="F77" s="77" t="n"/>
+      <x:c r="E77" s="77"/>
+      <x:c r="F77" s="77"/>
       <x:c r="G77" t="n">
         <x:v>77</x:v>
       </x:c>
@@ -5097,7 +5270,7 @@
       <x:c r="L77" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M77" s="77" t="n"/>
+      <x:c r="M77" s="77"/>
       <x:c r="N77" t="n">
         <x:v>222</x:v>
       </x:c>
@@ -5107,7 +5280,7 @@
       <x:c r="P77" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="Q77">
+      <x:c r="Q77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R77" t="n">
@@ -5116,22 +5289,24 @@
       <x:c r="S77" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T77" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U77"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="77" t="n"/>
+      <x:c r="A78" s="77"/>
       <x:c r="B78" s="115" t="n">
         <x:v>10074</x:v>
       </x:c>
-      <x:c r="C78" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm910</x:t>
-        </x:is>
+      <x:c r="C78" s="77" t="str">
+        <x:v>btm910</x:v>
       </x:c>
       <x:c r="D78" s="115" t="n">
         <x:v>20074</x:v>
       </x:c>
-      <x:c r="E78" s="77" t="n"/>
-      <x:c r="F78" s="77" t="n"/>
+      <x:c r="E78" s="77"/>
+      <x:c r="F78" s="77"/>
       <x:c r="G78" t="n">
         <x:v>93.5</x:v>
       </x:c>
@@ -5150,7 +5325,7 @@
       <x:c r="L78" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M78" s="77" t="n"/>
+      <x:c r="M78" s="77"/>
       <x:c r="N78" t="n">
         <x:v>249</x:v>
       </x:c>
@@ -5160,7 +5335,7 @@
       <x:c r="P78" t="n">
         <x:v>109.5</x:v>
       </x:c>
-      <x:c r="Q78">
+      <x:c r="Q78" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R78" t="n">
@@ -5169,22 +5344,24 @@
       <x:c r="S78" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T78" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U78"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="77" t="n"/>
+      <x:c r="A79" s="77"/>
       <x:c r="B79" s="115" t="n">
         <x:v>10075</x:v>
       </x:c>
-      <x:c r="C79" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm911</x:t>
-        </x:is>
+      <x:c r="C79" s="77" t="str">
+        <x:v>btm911</x:v>
       </x:c>
       <x:c r="D79" s="115" t="n">
         <x:v>20075</x:v>
       </x:c>
-      <x:c r="E79" s="77" t="n"/>
-      <x:c r="F79" s="77" t="n"/>
+      <x:c r="E79" s="77"/>
+      <x:c r="F79" s="77"/>
       <x:c r="G79" t="n">
         <x:v>25</x:v>
       </x:c>
@@ -5203,7 +5380,7 @@
       <x:c r="L79" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M79" s="77" t="n"/>
+      <x:c r="M79" s="77"/>
       <x:c r="N79" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -5213,7 +5390,7 @@
       <x:c r="P79" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="Q79">
+      <x:c r="Q79" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R79" t="n">
@@ -5222,22 +5399,24 @@
       <x:c r="S79" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T79" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U79"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="77" t="n"/>
+      <x:c r="A80" s="77"/>
       <x:c r="B80" s="115" t="n">
         <x:v>10076</x:v>
       </x:c>
-      <x:c r="C80" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm912</x:t>
-        </x:is>
+      <x:c r="C80" s="77" t="str">
+        <x:v>btm912</x:v>
       </x:c>
       <x:c r="D80" s="115" t="n">
         <x:v>20076</x:v>
       </x:c>
-      <x:c r="E80" s="77" t="n"/>
-      <x:c r="F80" s="77" t="n"/>
+      <x:c r="E80" s="77"/>
+      <x:c r="F80" s="77"/>
       <x:c r="G80" t="n">
         <x:v>21</x:v>
       </x:c>
@@ -5256,7 +5435,7 @@
       <x:c r="L80" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M80" s="77" t="n"/>
+      <x:c r="M80" s="77"/>
       <x:c r="N80" t="n">
         <x:v>130</x:v>
       </x:c>
@@ -5266,7 +5445,7 @@
       <x:c r="P80" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="Q80">
+      <x:c r="Q80" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R80" t="n">
@@ -5275,22 +5454,24 @@
       <x:c r="S80" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T80" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U80"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="77" t="n"/>
+      <x:c r="A81" s="77"/>
       <x:c r="B81" s="115" t="n">
         <x:v>10077</x:v>
       </x:c>
-      <x:c r="C81" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm913</x:t>
-        </x:is>
+      <x:c r="C81" s="77" t="str">
+        <x:v>btm913</x:v>
       </x:c>
       <x:c r="D81" s="115" t="n">
         <x:v>20077</x:v>
       </x:c>
-      <x:c r="E81" s="77" t="n"/>
-      <x:c r="F81" s="77" t="n"/>
+      <x:c r="E81" s="77"/>
+      <x:c r="F81" s="77"/>
       <x:c r="G81" t="n">
         <x:v>71.5</x:v>
       </x:c>
@@ -5309,7 +5490,7 @@
       <x:c r="L81" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M81" s="77" t="n"/>
+      <x:c r="M81" s="77"/>
       <x:c r="N81" t="n">
         <x:v>295</x:v>
       </x:c>
@@ -5319,7 +5500,7 @@
       <x:c r="P81" t="n">
         <x:v>132.5</x:v>
       </x:c>
-      <x:c r="Q81">
+      <x:c r="Q81" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R81" t="n">
@@ -5328,22 +5509,24 @@
       <x:c r="S81" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T81" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U81"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="77" t="n"/>
+      <x:c r="A82" s="77"/>
       <x:c r="B82" s="115" t="n">
         <x:v>10078</x:v>
       </x:c>
-      <x:c r="C82" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm914</x:t>
-        </x:is>
+      <x:c r="C82" s="77" t="str">
+        <x:v>btm914</x:v>
       </x:c>
       <x:c r="D82" s="115" t="n">
         <x:v>20078</x:v>
       </x:c>
-      <x:c r="E82" s="77" t="n"/>
-      <x:c r="F82" s="77" t="n"/>
+      <x:c r="E82" s="77"/>
+      <x:c r="F82" s="77"/>
       <x:c r="G82" t="n">
         <x:v>175.5</x:v>
       </x:c>
@@ -5362,7 +5545,7 @@
       <x:c r="L82" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M82" s="77" t="n"/>
+      <x:c r="M82" s="77"/>
       <x:c r="N82" t="n">
         <x:v>268</x:v>
       </x:c>
@@ -5372,7 +5555,7 @@
       <x:c r="P82" t="n">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="Q82">
+      <x:c r="Q82" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R82" t="n">
@@ -5381,22 +5564,24 @@
       <x:c r="S82" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T82" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U82"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="77" t="n"/>
+      <x:c r="A83" s="77"/>
       <x:c r="B83" s="115" t="n">
         <x:v>10079</x:v>
       </x:c>
-      <x:c r="C83" s="77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">btm2000</x:t>
-        </x:is>
+      <x:c r="C83" s="77" t="str">
+        <x:v>btm2000</x:v>
       </x:c>
       <x:c r="D83" s="115" t="n">
         <x:v>20079</x:v>
       </x:c>
-      <x:c r="E83" s="77" t="n"/>
-      <x:c r="F83" s="77" t="n"/>
+      <x:c r="E83" s="77"/>
+      <x:c r="F83" s="77"/>
       <x:c r="G83" t="n">
         <x:v>93</x:v>
       </x:c>
@@ -5415,7 +5600,7 @@
       <x:c r="L83" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M83" s="77" t="n"/>
+      <x:c r="M83" s="77"/>
       <x:c r="N83" t="n">
         <x:v>222</x:v>
       </x:c>
@@ -5425,7 +5610,7 @@
       <x:c r="P83" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="Q83">
+      <x:c r="Q83" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R83" t="n">
@@ -5434,11 +5619,92 @@
       <x:c r="S83" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T83" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U83"/>
     </x:row>
     <x:row r="84">
+      <x:c r="A84"/>
+      <x:c r="B84"/>
+      <x:c r="C84"/>
+      <x:c r="D84"/>
+      <x:c r="E84"/>
+      <x:c r="F84"/>
+      <x:c r="G84"/>
+      <x:c r="H84"/>
+      <x:c r="I84"/>
+      <x:c r="J84"/>
+      <x:c r="K84"/>
+      <x:c r="L84"/>
+      <x:c r="M84"/>
+      <x:c r="N84"/>
+      <x:c r="O84"/>
+      <x:c r="P84"/>
       <x:c r="Q84"/>
       <x:c r="R84"/>
       <x:c r="S84"/>
+      <x:c r="T84"/>
+      <x:c r="U84"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="B85" t="n">
+        <x:v>40101</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>btm311</x:v>
+      </x:c>
+      <x:c r="D85" t="n">
+        <x:v>20032</x:v>
+      </x:c>
+      <x:c r="E85" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F85" t="n">
+        <x:v>20002</x:v>
+      </x:c>
+      <x:c r="G85" t="n">
+        <x:v>73.011</x:v>
+      </x:c>
+      <x:c r="H85" t="n">
+        <x:v>73.011</x:v>
+      </x:c>
+      <x:c r="I85" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J85" t="n">
+        <x:v>-9.4</x:v>
+      </x:c>
+      <x:c r="K85" t="n">
+        <x:v>80.2</x:v>
+      </x:c>
+      <x:c r="L85" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M85" t="str">
+        <x:v>Ground</x:v>
+      </x:c>
+      <x:c r="N85" t="n">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="O85" t="n">
+        <x:v>-9.4</x:v>
+      </x:c>
+      <x:c r="P85" t="n">
+        <x:v>80.2</x:v>
+      </x:c>
+      <x:c r="Q85" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R85" t="n">
+        <x:v>-9.4</x:v>
+      </x:c>
+      <x:c r="S85" t="n">
+        <x:v>80.2</x:v>
+      </x:c>
+      <x:c r="T85" s="116" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
